--- a/Models/Молоко/results/Молоко - Результаты прогнозов ХВ.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[8444.94, 9839.59, 15952.39]</t>
+          <t>[22664.47, 22108.67, 16700.88]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[10829.7, 11876.6, 17387.5]</t>
+          <t>[22673.0, 22635.3, 18373.4]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1991.317088317923</v>
+        <v>1012.379724549841</v>
       </c>
       <c r="G2" t="n">
-        <v>1952.293112407377</v>
+        <v>735.8953664030014</v>
       </c>
       <c r="H2" t="n">
-        <v>15.8085674243482</v>
+        <v>3.822392867146614</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[11965.2, 19362.36, 23847.83]</t>
+          <t>[22116.73, 16706.45, 14464.08]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[11876.6, 17387.5, 20221.1]</t>
+          <t>[22635.3, 18373.4, 15949.9]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2384.748637254107</v>
+        <v>1323.541069360631</v>
       </c>
       <c r="G3" t="n">
-        <v>1896.727258384103</v>
+        <v>1223.778377021755</v>
       </c>
       <c r="H3" t="n">
-        <v>10.01308302447504</v>
+        <v>6.893039943178085</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[19247.39, 23707.56, 29991.84]</t>
+          <t>[17017.48, 14729.22, 15792.52]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[17387.5, 20221.1, 24058.8]</t>
+          <t>[18373.4, 15949.9, 16241.4]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4115.641012080618</v>
+        <v>1084.75306390019</v>
       </c>
       <c r="G4" t="n">
-        <v>3759.794418378749</v>
+        <v>1008.493483537076</v>
       </c>
       <c r="H4" t="n">
-        <v>17.5329829186627</v>
+        <v>5.932273497778277</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[21907.75, 27733.65, 31788.8]</t>
+          <t>[15660.77, 16781.84, 9323.12]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[20221.1, 24058.8, 28277.0]</t>
+          <t>[15949.9, 16241.4, 11378.1]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3092.036407030309</v>
+        <v>1238.092941306346</v>
       </c>
       <c r="G5" t="n">
-        <v>2957.767441371785</v>
+        <v>961.5187213499248</v>
       </c>
       <c r="H5" t="n">
-        <v>12.01159357751169</v>
+        <v>7.733720123839703</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[26034.58, 29857.09, 27484.33]</t>
+          <t>[17030.25, 9459.76, 10945.48]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[24058.8, 28277.0, 26267.7]</t>
+          <t>[16241.4, 11378.1, 12075.2]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1620.75929212982</v>
+        <v>1363.642958211546</v>
       </c>
       <c r="G6" t="n">
-        <v>1590.833075127741</v>
+        <v>1278.968786873972</v>
       </c>
       <c r="H6" t="n">
-        <v>6.143950012212405</v>
+        <v>10.35754511054865</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[28031.73, 25816.72, 22324.5]</t>
+          <t>[9108.42, 10542.06, 16907.71]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[28277.0, 26267.7, 22673.0]</t>
+          <t>[11378.1, 12075.2, 18113.7]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>358.2345475460864</v>
+        <v>1727.847311780771</v>
       </c>
       <c r="G7" t="n">
-        <v>348.2510971186178</v>
+        <v>1669.603422807868</v>
       </c>
       <c r="H7" t="n">
-        <v>1.37377646853684</v>
+        <v>13.10075707632676</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[25997.35, 22478.51, 21929.31]</t>
+          <t>[12569.27, 20128.17, 24637.97]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[26267.7, 22673.0, 22635.3]</t>
+          <t>[12075.2, 18113.7, 20536.1]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>450.6794458306506</v>
+        <v>2653.774139049491</v>
       </c>
       <c r="G8" t="n">
-        <v>390.2763427211491</v>
+        <v>2203.470774947846</v>
       </c>
       <c r="H8" t="n">
-        <v>1.668662199191914</v>
+        <v>11.72894054302284</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[22664.47, 22108.67, 16700.88]</t>
+          <t>[19500.29, 23875.57, 30013.06]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[22673.0, 22635.3, 18373.4]</t>
+          <t>[18113.7, 20536.1, 24905.7]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1012.379724549841</v>
+        <v>3612.929899426157</v>
       </c>
       <c r="G9" t="n">
-        <v>735.8953664030014</v>
+        <v>3277.80578992871</v>
       </c>
       <c r="H9" t="n">
-        <v>3.822392867146614</v>
+        <v>14.80772264730254</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[22116.73, 16706.45, 14464.08]</t>
+          <t>[22545.34, 28353.15, 32567.83]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[22635.3, 18373.4, 15949.9]</t>
+          <t>[20536.1, 24905.7, 28491.6]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1323.541069360631</v>
+        <v>3293.307052548909</v>
       </c>
       <c r="G10" t="n">
-        <v>1223.778377021755</v>
+        <v>3177.640843801637</v>
       </c>
       <c r="H10" t="n">
-        <v>6.893039943178085</v>
+        <v>12.64424831871005</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[17017.48, 14729.22, 15792.52]</t>
+          <t>[26342.74, 30274.67, 27884.25]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[18373.4, 15949.9, 16241.4]</t>
+          <t>[24905.7, 28491.6, 25379.9]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1084.75306390019</v>
+        <v>1959.268041076126</v>
       </c>
       <c r="G11" t="n">
-        <v>1008.493483537076</v>
+        <v>1908.15309582575</v>
       </c>
       <c r="H11" t="n">
-        <v>5.932273497778277</v>
+        <v>7.298534921319577</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[3016.51, 7332.02, 16007.98]</t>
+          <t>[18102.1, 17118.62, 13453.69]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[3531.8, 7660.0, 14235.9]</t>
+          <t>[19708.6, 18126.4, 14585.2]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1082.18323409649</v>
+        <v>1274.987841248867</v>
       </c>
       <c r="G12" t="n">
-        <v>871.7835566235402</v>
+        <v>1248.597351335965</v>
       </c>
       <c r="H12" t="n">
-        <v>10.43989827496651</v>
+        <v>7.156316442576414</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[7904.47, 17245.46, 14884.93]</t>
+          <t>[17827.3, 14005.19, 10630.23]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[7660.0, 14235.9, 12247.2]</t>
+          <t>[18126.4, 14585.2, 12179.5]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2314.792316018881</v>
+        <v>970.587139510581</v>
       </c>
       <c r="G13" t="n">
-        <v>1963.917496089244</v>
+        <v>809.4627788086121</v>
       </c>
       <c r="H13" t="n">
-        <v>15.28983711357455</v>
+        <v>6.115714389248927</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[16989.24, 14664.29, 19968.11]</t>
+          <t>[14117.33, 10714.86, 10576.68]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[14235.9, 12247.2, 15024.9]</t>
+          <t>[14585.2, 12179.5, 10873.8]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3552.394482247987</v>
+        <v>904.1273858820542</v>
       </c>
       <c r="G14" t="n">
-        <v>3371.21211929533</v>
+        <v>743.2061763506948</v>
       </c>
       <c r="H14" t="n">
-        <v>23.99225658707778</v>
+        <v>5.988546959420027</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[13494.4, 18390.37, 28995.03]</t>
+          <t>[10883.84, 10741.53, 2985.06]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[12247.2, 15024.9, 26224.1]</t>
+          <t>[12179.5, 10873.8, 3645.1]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2617.883267672196</v>
+        <v>842.9872987755923</v>
       </c>
       <c r="G15" t="n">
-        <v>2461.1990542888</v>
+        <v>695.990889252017</v>
       </c>
       <c r="H15" t="n">
-        <v>14.38305253438693</v>
+        <v>9.987349810877655</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[17558.92, 27703.41, 21694.0]</t>
+          <t>[11339.71, 3148.32, 7564.77]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[15024.9, 26224.1, 22111.2]</t>
+          <t>[10873.8, 3645.1, 7802.9]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1711.10785522345</v>
+        <v>416.5585525498342</v>
       </c>
       <c r="G16" t="n">
-        <v>1476.843564194329</v>
+        <v>400.2716250859078</v>
       </c>
       <c r="H16" t="n">
-        <v>8.131110821181805</v>
+        <v>6.988371477011553</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[25688.22, 20132.06, 17219.68]</t>
+          <t>[3086.79, 7417.03, 15932.12]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[26224.1, 22111.2, 19708.6]</t>
+          <t>[3645.1, 7802.9, 14584.2]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1861.800127183873</v>
+        <v>871.3022934428121</v>
       </c>
       <c r="G17" t="n">
-        <v>1667.980371971037</v>
+        <v>764.0351865960957</v>
       </c>
       <c r="H17" t="n">
-        <v>7.874306580072581</v>
+        <v>9.834800678556444</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[20336.06, 17394.02, 16453.62]</t>
+          <t>[8038.01, 17253.66, 14887.21]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[22111.2, 19708.6, 18126.4]</t>
+          <t>[7802.9, 14584.2, 12551.0]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1941.354155167637</v>
+        <v>2052.572795087929</v>
       </c>
       <c r="G18" t="n">
-        <v>1920.830820729541</v>
+        <v>1746.925627467825</v>
       </c>
       <c r="H18" t="n">
-        <v>9.66687590434735</v>
+        <v>13.31019690472051</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[18102.1, 17118.62, 13453.69]</t>
+          <t>[17010.56, 14674.96, 19770.96]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[19708.6, 18126.4, 14585.2]</t>
+          <t>[14584.2, 12551.0, 15396.2]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1274.987841248867</v>
+        <v>3137.775097391785</v>
       </c>
       <c r="G19" t="n">
-        <v>1248.597351335965</v>
+        <v>2975.024182218716</v>
       </c>
       <c r="H19" t="n">
-        <v>7.156316442576414</v>
+        <v>20.65801360743762</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[17827.3, 14005.19, 10630.23]</t>
+          <t>[13635.64, 18380.63, 29275.47]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[18126.4, 14585.2, 12179.5]</t>
+          <t>[12551.0, 15396.2, 26838.1]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>970.587139510581</v>
+        <v>2311.137620103853</v>
       </c>
       <c r="G20" t="n">
-        <v>809.4627788086121</v>
+        <v>2168.816050286125</v>
       </c>
       <c r="H20" t="n">
-        <v>6.115714389248927</v>
+        <v>12.36928992589443</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[14117.33, 10714.86, 10576.68]</t>
+          <t>[17659.84, 28137.71, 22193.22]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[14585.2, 12179.5, 10873.8]</t>
+          <t>[15396.2, 26838.1, 22505.1]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>904.1273858820542</v>
+        <v>1517.710052645939</v>
       </c>
       <c r="G21" t="n">
-        <v>743.2061763506948</v>
+        <v>1291.710844479894</v>
       </c>
       <c r="H21" t="n">
-        <v>5.988546959420027</v>
+        <v>6.976945749336784</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[12576.13, 11295.38, 14608.89]</t>
+          <t>[30351.43, 32806.6, 27130.53]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[18455.6, 15274.2, 18596.8]</t>
+          <t>[32883.5, 32588.5, 30090.5]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4701.157484694608</v>
+        <v>2252.432686041746</v>
       </c>
       <c r="G22" t="n">
-        <v>4615.401246170691</v>
+        <v>1903.380114238687</v>
       </c>
       <c r="H22" t="n">
-        <v>26.45024894807459</v>
+        <v>6.068756819322975</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[15839.7, 20763.77, 22955.47]</t>
+          <t>[34855.15, 28780.21, 23228.45]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[15274.2, 18596.8, 19186.9]</t>
+          <t>[32588.5, 30090.5, 22030.8]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2530.983863211814</v>
+        <v>1662.219707753142</v>
       </c>
       <c r="G23" t="n">
-        <v>2167.010749331921</v>
+        <v>1591.528914179459</v>
       </c>
       <c r="H23" t="n">
-        <v>11.66534225164009</v>
+        <v>5.582033732374496</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[20209.51, 22343.17, 27772.34]</t>
+          <t>[27528.49, 22120.45, 12604.07]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[18596.8, 19186.9, 22461.3]</t>
+          <t>[30090.5, 22030.8, 15652.0]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3686.465725651238</v>
+        <v>2299.406855407844</v>
       </c>
       <c r="G24" t="n">
-        <v>3360.009427584188</v>
+        <v>1899.86467042256</v>
       </c>
       <c r="H24" t="n">
-        <v>16.25581271024359</v>
+        <v>9.464801645682941</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[20998.09, 26096.76, 29658.42]</t>
+          <t>[23512.06, 13298.66, 20427.62]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[19186.9, 22461.3, 32608.5]</t>
+          <t>[22030.8, 15652.0, 18568.9]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2898.270704925981</v>
+        <v>1931.074313050073</v>
       </c>
       <c r="G25" t="n">
-        <v>2798.908393780359</v>
+        <v>1897.770255422727</v>
       </c>
       <c r="H25" t="n">
-        <v>11.55736837553367</v>
+        <v>10.58959511164887</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[24374.96, 27655.77, 23897.68]</t>
+          <t>[12652.09, 19484.41, 16485.0]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[22461.3, 32608.5, 29724.3]</t>
+          <t>[15652.0, 18568.9, 16396.4]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4551.231760214368</v>
+        <v>1811.579536111245</v>
       </c>
       <c r="G26" t="n">
-        <v>4231.003489488991</v>
+        <v>1334.673304533378</v>
       </c>
       <c r="H26" t="n">
-        <v>14.43682900835564</v>
+        <v>8.212336710627232</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[25956.96, 22437.93, 23548.04]</t>
+          <t>[22541.22, 19110.77, 24661.59]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[32608.5, 29724.3, 32883.5]</t>
+          <t>[18568.9, 16396.4, 20150.5]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7841.872837149775</v>
+        <v>3807.757799252847</v>
       </c>
       <c r="G27" t="n">
-        <v>7757.788504398922</v>
+        <v>3732.593442108058</v>
       </c>
       <c r="H27" t="n">
-        <v>24.43361230330491</v>
+        <v>20.1113301001772</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[26472.67, 27874.72, 30008.21]</t>
+          <t>[16535.36, 21355.14, 23473.76]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[29724.3, 32883.5, 32588.5]</t>
+          <t>[16396.4, 20150.5, 19816.5]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3755.834089508766</v>
+        <v>2224.560767837327</v>
       </c>
       <c r="G28" t="n">
-        <v>3613.56635190982</v>
+        <v>1666.952935289321</v>
       </c>
       <c r="H28" t="n">
-        <v>11.3629945116768</v>
+        <v>8.427113527641977</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[30351.43, 32806.6, 27130.53]</t>
+          <t>[21216.9, 23322.32, 29049.45]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[32883.5, 32588.5, 30090.5]</t>
+          <t>[20150.5, 19816.5, 23213.0]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2252.432686041746</v>
+        <v>3978.780974650515</v>
       </c>
       <c r="G29" t="n">
-        <v>1903.380114238687</v>
+        <v>3469.556156587974</v>
       </c>
       <c r="H29" t="n">
-        <v>6.068756819322975</v>
+        <v>16.04220379251888</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[34855.15, 28780.21, 23228.45]</t>
+          <t>[22429.67, 27934.19, 34101.28]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[32588.5, 30090.5, 22030.8]</t>
+          <t>[19816.5, 23213.0, 33260.5]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1662.219707753142</v>
+        <v>3153.052179441718</v>
       </c>
       <c r="G30" t="n">
-        <v>1591.528914179459</v>
+        <v>2725.047768875438</v>
       </c>
       <c r="H30" t="n">
-        <v>5.582033732374496</v>
+        <v>12.01776007910523</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[27528.49, 22120.45, 12604.07]</t>
+          <t>[25414.76, 30908.6, 26138.94]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[30090.5, 22030.8, 15652.0]</t>
+          <t>[23213.0, 33260.5, 31438.9]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2299.406855407844</v>
+        <v>3580.910772780208</v>
       </c>
       <c r="G31" t="n">
-        <v>1899.86467042256</v>
+        <v>3284.539380643878</v>
       </c>
       <c r="H31" t="n">
-        <v>9.464801645682941</v>
+        <v>11.13804607855826</v>
       </c>
     </row>
     <row r="32">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[740.39, 1028.08, 1627.55]</t>
+          <t>[3074.53, 3141.43, 1464.23]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1105.5, 1143.8, 1759.6]</t>
+          <t>[3263.7, 3272.5, 1500.4]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>233.9054084339424</v>
+        <v>134.5024771679581</v>
       </c>
       <c r="G32" t="n">
-        <v>204.295034696361</v>
+        <v>118.8019723836939</v>
       </c>
       <c r="H32" t="n">
-        <v>16.88294944276191</v>
+        <v>4.070597942339575</v>
       </c>
     </row>
     <row r="33">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[1388.16, 2155.27, 3735.61]</t>
+          <t>[3286.37, 1532.5, 2265.95]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[1143.8, 1759.6, 2706.1]</t>
+          <t>[3272.5, 1500.4, 2262.7]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>652.2147135142827</v>
+        <v>20.27798681757515</v>
       </c>
       <c r="G33" t="n">
-        <v>556.5106747864722</v>
+        <v>16.40885713927211</v>
       </c>
       <c r="H33" t="n">
-        <v>27.29789701629766</v>
+        <v>0.9024299652295537</v>
       </c>
     </row>
     <row r="34">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[1876.19, 3256.47, 6194.64]</t>
+          <t>[1527.57, 2258.68, 2412.19]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1759.6, 2706.1, 5069.0]</t>
+          <t>[1500.4, 2262.7, 2702.3]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>726.5365976426984</v>
+        <v>168.245280355892</v>
       </c>
       <c r="G34" t="n">
-        <v>597.5319054881976</v>
+        <v>107.0991970171687</v>
       </c>
       <c r="H34" t="n">
-        <v>16.39005108118051</v>
+        <v>4.241343992069457</v>
       </c>
     </row>
     <row r="35">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[3101.53, 5889.87, 3923.51]</t>
+          <t>[2228.75, 2381.15, 920.13]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[2706.1, 5069.0, 3739.6]</t>
+          <t>[2262.7, 2702.3, 1102.6]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>536.6602512548</v>
+        <v>214.1547491212919</v>
       </c>
       <c r="G35" t="n">
-        <v>466.7372195111186</v>
+        <v>179.1919567706281</v>
       </c>
       <c r="H35" t="n">
-        <v>11.90814918499358</v>
+        <v>9.978071318707983</v>
       </c>
     </row>
     <row r="36">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[5301.0, 3519.6, 2585.0]</t>
+          <t>[2408.25, 930.55, 1106.32]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[5069.0, 3739.6, 2804.7]</t>
+          <t>[2702.3, 1102.6, 1147.4]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>223.9701778716899</v>
+        <v>198.1181246800315</v>
       </c>
       <c r="G36" t="n">
-        <v>223.8969070634757</v>
+        <v>169.0588905715549</v>
       </c>
       <c r="H36" t="n">
-        <v>6.097619423689749</v>
+        <v>10.02182902679264</v>
       </c>
     </row>
     <row r="37">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[3396.09, 2496.64, 2770.0]</t>
+          <t>[1007.34, 1192.36, 1914.88]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[3739.6, 2804.7, 3263.7]</t>
+          <t>[1102.6, 1147.4, 1787.2]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>390.1458309161349</v>
+        <v>95.56687992765472</v>
       </c>
       <c r="G37" t="n">
-        <v>381.756885882345</v>
+        <v>89.30214222157811</v>
       </c>
       <c r="H37" t="n">
-        <v>11.76548613925116</v>
+        <v>6.567528529809226</v>
       </c>
     </row>
     <row r="38">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[2679.54, 2971.37, 3034.74]</t>
+          <t>[1283.98, 2056.28, 3481.67]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[2804.7, 3263.7, 3272.5]</t>
+          <t>[1147.4, 1787.2, 2839.9]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>229.2392849834874</v>
+        <v>409.4397922908844</v>
       </c>
       <c r="G38" t="n">
-        <v>218.4176940921622</v>
+        <v>349.1419581569863</v>
       </c>
       <c r="H38" t="n">
-        <v>6.895007987140526</v>
+        <v>16.51915220590616</v>
       </c>
     </row>
     <row r="39">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[3074.53, 3141.43, 1464.23]</t>
+          <t>[1896.6, 3215.07, 6253.51]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[3263.7, 3272.5, 1500.4]</t>
+          <t>[1787.2, 2839.9, 5432.7]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>134.5024771679581</v>
+        <v>524.8669258390285</v>
       </c>
       <c r="G39" t="n">
-        <v>118.8019723836939</v>
+        <v>435.1279021839977</v>
       </c>
       <c r="H39" t="n">
-        <v>4.070597942339575</v>
+        <v>11.48024288878907</v>
       </c>
     </row>
     <row r="40">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[3286.37, 1532.5, 2265.95]</t>
+          <t>[3078.13, 5983.26, 4149.28]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[3272.5, 1500.4, 2262.7]</t>
+          <t>[2839.9, 5432.7, 4032.2]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20.27798681757515</v>
+        <v>352.8816666566617</v>
       </c>
       <c r="G40" t="n">
-        <v>16.40885713927211</v>
+        <v>301.9553192314825</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9024299652295537</v>
+        <v>7.142131529756086</v>
       </c>
     </row>
     <row r="41">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[1527.57, 2258.68, 2412.19]</t>
+          <t>[5633.44, 3899.91, 2829.38]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[1500.4, 2262.7, 2702.3]</t>
+          <t>[5432.7, 4032.2, 2987.3]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>168.245280355892</v>
+        <v>166.067408416983</v>
       </c>
       <c r="G41" t="n">
-        <v>107.0991970171687</v>
+        <v>163.6494734511133</v>
       </c>
       <c r="H41" t="n">
-        <v>4.241343992069457</v>
+        <v>4.08740181921482</v>
       </c>
     </row>
     <row r="42">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[10117.07, 12068.94, 18124.49]</t>
+          <t>[24783.07, 21703.66, 16918.22]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[10951.0, 11242.4, 14881.1]</t>
+          <t>[25528.8, 21278.6, 19066.4]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1991.500355713619</v>
+        <v>1335.59821385506</v>
       </c>
       <c r="G42" t="n">
-        <v>1634.622172164024</v>
+        <v>1106.323593123627</v>
       </c>
       <c r="H42" t="n">
-        <v>12.25416823926745</v>
+        <v>5.395188611756932</v>
       </c>
     </row>
     <row r="43">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[13054.59, 19588.7, 24262.74]</t>
+          <t>[22351.42, 17419.19, 15900.99]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[11242.4, 14881.1, 18177.3]</t>
+          <t>[21278.6, 19066.4, 19393.8]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4563.55628804852</v>
+        <v>2314.012258503243</v>
       </c>
       <c r="G43" t="n">
-        <v>4201.743133928807</v>
+        <v>2070.947551440418</v>
       </c>
       <c r="H43" t="n">
-        <v>27.07740853361412</v>
+        <v>10.56368560878907</v>
       </c>
     </row>
     <row r="44">
@@ -1990,32 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[16890.91, 20948.07, 25727.8]</t>
+          <t>[16589.16, 15150.02, 14126.39]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[14881.1, 18177.3, 19851.9]</t>
+          <t>[19066.4, 19393.8, 25435.0]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3926.09669980203</v>
+        <v>7118.778159812208</v>
       </c>
       <c r="G44" t="n">
-        <v>3552.159139047542</v>
+        <v>6009.875972654673</v>
       </c>
       <c r="H44" t="n">
-        <v>19.44915808926697</v>
+        <v>26.44522011873974</v>
       </c>
     </row>
     <row r="45">
@@ -2026,32 +2026,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[18474.82, 22714.55, 27456.76]</t>
+          <t>[17389.92, 16194.7, 9573.53]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[18177.3, 19851.9, 26546.0]</t>
+          <t>[19393.8, 25435.0, 11925.9]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1742.867997034406</v>
+        <v>5625.312278565827</v>
       </c>
       <c r="G45" t="n">
-        <v>1356.975151554182</v>
+        <v>4532.186209897958</v>
       </c>
       <c r="H45" t="n">
-        <v>6.495882390779782</v>
+        <v>22.12885977263973</v>
       </c>
     </row>
     <row r="46">
@@ -2062,32 +2062,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[22351.94, 27023.04, 26224.54]</t>
+          <t>[18042.75, 10655.28, 12516.76]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[19851.9, 26546.0, 26667.5]</t>
+          <t>[25435.0, 11925.9, 13309.0]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1491.531465547764</v>
+        <v>4354.596269117065</v>
       </c>
       <c r="G46" t="n">
-        <v>1140.014238397124</v>
+        <v>3151.704505866048</v>
       </c>
       <c r="H46" t="n">
-        <v>5.350516382128221</v>
+        <v>15.22342265402786</v>
       </c>
     </row>
     <row r="47">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[24023.24, 23338.33, 21715.53]</t>
+          <t>[14973.92, 17539.59, 25923.27]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[26546.0, 26667.5, 25528.8]</t>
+          <t>[11925.9, 13309.0, 17781.5]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3265.409283363207</v>
+        <v>5582.018316291018</v>
       </c>
       <c r="G47" t="n">
-        <v>3221.731847316324</v>
+        <v>5140.127883684359</v>
       </c>
       <c r="H47" t="n">
-        <v>12.308154233837</v>
+        <v>34.37777265257507</v>
       </c>
     </row>
     <row r="48">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[25765.61, 23951.95, 20982.3]</t>
+          <t>[13995.94, 20724.9, 25616.24]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[26667.5, 25528.8, 21278.6]</t>
+          <t>[13309.0, 17781.5, 21818.7]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1062.644290011611</v>
+        <v>2802.189474373076</v>
       </c>
       <c r="G48" t="n">
-        <v>925.0109641731736</v>
+        <v>2475.959595860895</v>
       </c>
       <c r="H48" t="n">
-        <v>3.650393409312283</v>
+        <v>13.03986599694575</v>
       </c>
     </row>
     <row r="49">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[24783.07, 21703.66, 16918.22]</t>
+          <t>[19715.64, 24376.98, 29545.72]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[25528.8, 21278.6, 19066.4]</t>
+          <t>[17781.5, 21818.7, 24180.0]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1335.59821385506</v>
+        <v>3609.09409423835</v>
       </c>
       <c r="G49" t="n">
-        <v>1106.323593123627</v>
+        <v>3286.04746525211</v>
       </c>
       <c r="H49" t="n">
-        <v>5.395188611756932</v>
+        <v>14.93105912426995</v>
       </c>
     </row>
     <row r="50">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[22351.42, 17419.19, 15900.99]</t>
+          <t>[22004.65, 26690.97, 32537.66]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[21278.6, 19066.4, 19393.8]</t>
+          <t>[21818.7, 24180.0, 30155.4]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2314.012258503243</v>
+        <v>2001.223041380703</v>
       </c>
       <c r="G50" t="n">
-        <v>2070.947551440418</v>
+        <v>1693.056961506026</v>
       </c>
       <c r="H50" t="n">
-        <v>10.56368560878907</v>
+        <v>6.378883787759921</v>
       </c>
     </row>
     <row r="51">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[16589.16, 15150.02, 14126.39]</t>
+          <t>[26468.92, 32267.91, 31370.09]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[19066.4, 19393.8, 25435.0]</t>
+          <t>[24180.0, 30155.4, 28246.7]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>7118.778159812208</v>
+        <v>2546.72556570955</v>
       </c>
       <c r="G51" t="n">
-        <v>6009.875972654673</v>
+        <v>2508.274320573028</v>
       </c>
       <c r="H51" t="n">
-        <v>26.44522011873974</v>
+        <v>9.176378207770508</v>
       </c>
     </row>
     <row r="52">
@@ -2278,32 +2278,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[9.4, 9.85, 1.27]</t>
+          <t>[30.82, 30.94, 100.99]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[48.2, 48.3, 16.1]</t>
+          <t>[27.5, 22.9, 28.7]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>32.67790992041576</v>
+        <v>42.03969039392339</v>
       </c>
       <c r="G52" t="n">
-        <v>30.69131227990047</v>
+        <v>27.88502694925249</v>
       </c>
       <c r="H52" t="n">
-        <v>84.06119550633781</v>
+        <v>99.6947532099099</v>
       </c>
     </row>
     <row r="53">
@@ -2314,32 +2314,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[23.94, 18.49, 28.26]</t>
+          <t>[29.37, 96.0, 62.73]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[48.3, 16.1, 28.6]</t>
+          <t>[22.9, 28.7, 28.2]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>14.13211082828699</v>
+        <v>43.83314330438734</v>
       </c>
       <c r="G53" t="n">
-        <v>9.027878575229707</v>
+        <v>36.10083557115062</v>
       </c>
       <c r="H53" t="n">
-        <v>22.14675241453296</v>
+        <v>128.4006052283225</v>
       </c>
     </row>
     <row r="54">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[26.41, 40.03, 57.21]</t>
+          <t>[85.86, 56.12, 43.08]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[16.1, 28.6, 29.1]</t>
+          <t>[28.7, 28.2, 38.6]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>18.50496042837845</v>
+        <v>36.82158211878905</v>
       </c>
       <c r="G54" t="n">
-        <v>16.61942736181672</v>
+        <v>29.85544384551716</v>
       </c>
       <c r="H54" t="n">
-        <v>66.88011678668816</v>
+        <v>103.2668472568569</v>
       </c>
     </row>
     <row r="55">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[31.7, 45.49, 50.82]</t>
+          <t>[33.1, 25.43, 12.41]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[28.6, 29.1, 27.3]</t>
+          <t>[28.2, 38.6, 24.9]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>16.64685982961634</v>
+        <v>10.85188567775297</v>
       </c>
       <c r="G55" t="n">
-        <v>14.33624388450521</v>
+        <v>10.18446073258129</v>
       </c>
       <c r="H55" t="n">
-        <v>51.10392317904476</v>
+        <v>33.87781595135284</v>
       </c>
     </row>
     <row r="56">
@@ -2422,32 +2422,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[43.47, 48.6, 46.74]</t>
+          <t>[23.4, 11.39, 8.26]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[29.1, 27.3, 28.4]</t>
+          <t>[38.6, 24.9, 25.7]</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>18.22304765386492</v>
+        <v>15.46876335131856</v>
       </c>
       <c r="G56" t="n">
-        <v>18.00090875998636</v>
+        <v>15.38448681740514</v>
       </c>
       <c r="H56" t="n">
-        <v>63.98483334396706</v>
+        <v>53.83505330066577</v>
       </c>
     </row>
     <row r="57">
@@ -2458,32 +2458,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[40.73, 39.22, 39.35]</t>
+          <t>[14.65, 10.66, 7.46]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[27.3, 28.4, 27.5]</t>
+          <t>[24.9, 25.7, 25.1]</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>12.08258631481039</v>
+        <v>14.63432918458035</v>
       </c>
       <c r="G57" t="n">
-        <v>12.03488015824506</v>
+        <v>14.31100758266005</v>
       </c>
       <c r="H57" t="n">
-        <v>43.46668365826012</v>
+        <v>56.65913623505398</v>
       </c>
     </row>
     <row r="58">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[32.75, 32.91, 33.02]</t>
+          <t>[13.81, 9.72, 15.4]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[28.4, 27.5, 22.9]</t>
+          <t>[25.7, 25.1, 27.8]</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>7.08652199831678</v>
+        <v>13.31077937593306</v>
       </c>
       <c r="G58" t="n">
-        <v>6.627625531973898</v>
+        <v>13.22124677368034</v>
       </c>
       <c r="H58" t="n">
-        <v>26.39797701721082</v>
+        <v>50.70683726916666</v>
       </c>
     </row>
     <row r="59">
@@ -2530,32 +2530,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[30.82, 30.94, 100.99]</t>
+          <t>[13.33, 20.88, 29.16]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[27.5, 22.9, 28.7]</t>
+          <t>[25.1, 27.8, 29.8]</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>42.03969039392339</v>
+        <v>7.89145937178141</v>
       </c>
       <c r="G59" t="n">
-        <v>27.88502694925249</v>
+        <v>6.442045730593706</v>
       </c>
       <c r="H59" t="n">
-        <v>99.6947532099099</v>
+        <v>24.63969140013196</v>
       </c>
     </row>
     <row r="60">
@@ -2566,32 +2566,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[29.37, 96.0, 62.73]</t>
+          <t>[28.96, 40.22, 44.2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[22.9, 28.7, 28.2]</t>
+          <t>[27.8, 29.8, 27.9]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>43.83314330438734</v>
+        <v>11.18690189592924</v>
       </c>
       <c r="G60" t="n">
-        <v>36.10083557115062</v>
+        <v>9.291791961371699</v>
       </c>
       <c r="H60" t="n">
-        <v>128.4006052283225</v>
+        <v>32.51552471858682</v>
       </c>
     </row>
     <row r="61">
@@ -2602,32 +2602,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[85.86, 56.12, 43.08]</t>
+          <t>[39.36, 43.27, 41.96]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[28.7, 28.2, 38.6]</t>
+          <t>[29.8, 27.9, 27.1]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>36.82158211878905</v>
+        <v>13.52034068658035</v>
       </c>
       <c r="G61" t="n">
-        <v>29.85544384551716</v>
+        <v>13.26297596524348</v>
       </c>
       <c r="H61" t="n">
-        <v>103.2668472568569</v>
+        <v>47.33312657794816</v>
       </c>
     </row>
     <row r="62">
@@ -2638,32 +2638,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[13.06, 12.89, 12.72]</t>
+          <t>[25.16, 14.66, 11.07]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[11.2, 9.7, 11.3]</t>
+          <t>[25.0, 17.4, 12.4]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.285498779364127</v>
+        <v>1.760062331650376</v>
       </c>
       <c r="G62" t="n">
-        <v>2.157917016810931</v>
+        <v>1.409139763938446</v>
       </c>
       <c r="H62" t="n">
-        <v>20.69893229979504</v>
+        <v>9.028182122970469</v>
       </c>
     </row>
     <row r="63">
@@ -2674,32 +2674,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[12.59, 12.42, 18.82]</t>
+          <t>[14.64, 11.06, 5.48]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[9.7, 11.3, 20.9]</t>
+          <t>[17.4, 12.4, 6.6]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.152503392804216</v>
+        <v>1.883831756615806</v>
       </c>
       <c r="G63" t="n">
-        <v>2.028668620043797</v>
+        <v>1.737874934214112</v>
       </c>
       <c r="H63" t="n">
-        <v>16.54359326494045</v>
+        <v>14.52464555268898</v>
       </c>
     </row>
     <row r="64">
@@ -2710,32 +2710,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[11.95, 18.13, 19.41]</t>
+          <t>[11.38, 5.65, 0.2]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[11.3, 20.9, 19.9]</t>
+          <t>[12.4, 6.6, 0.2]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.665215255281197</v>
+        <v>0.8020441827380979</v>
       </c>
       <c r="G64" t="n">
-        <v>1.303611250160525</v>
+        <v>0.6558905264399228</v>
       </c>
       <c r="H64" t="n">
-        <v>7.1634934174319</v>
+        <v>8.235922933985748</v>
       </c>
     </row>
     <row r="65">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[17.99, 19.26, 22.7]</t>
+          <t>[5.73, 0.22, 10.65]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[20.9, 19.9, 18.0]</t>
+          <t>[6.6, 0.2, 6.6]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.213000583549044</v>
+        <v>2.389851907053365</v>
       </c>
       <c r="G65" t="n">
-        <v>2.750485763899889</v>
+        <v>1.644317828047412</v>
       </c>
       <c r="H65" t="n">
-        <v>14.41905757469184</v>
+        <v>27.88993738186118</v>
       </c>
     </row>
     <row r="66">
@@ -2782,32 +2782,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[19.67, 23.2, 31.45]</t>
+          <t>[0.24, 10.85, 9.75]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[19.9, 18.0, 25.1]</t>
+          <t>[0.2, 6.6, 6.3]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4.738448266911496</v>
+        <v>3.159802006869937</v>
       </c>
       <c r="G66" t="n">
-        <v>3.926084934523132</v>
+        <v>2.57943170110086</v>
       </c>
       <c r="H66" t="n">
-        <v>18.44464056914465</v>
+        <v>46.34388950311823</v>
       </c>
     </row>
     <row r="67">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[23.23, 31.5, 26.97]</t>
+          <t>[10.79, 9.7, 11.36]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[18.0, 25.1, 25.0]</t>
+          <t>[6.6, 6.3, 6.8]</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4.906148512440853</v>
+        <v>4.07775245892582</v>
       </c>
       <c r="G67" t="n">
-        <v>4.53412076325574</v>
+        <v>4.048674815570318</v>
       </c>
       <c r="H67" t="n">
-        <v>20.81694389318972</v>
+        <v>61.4826712332047</v>
       </c>
     </row>
     <row r="68">
@@ -2854,32 +2854,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[30.36, 25.99, 15.17]</t>
+          <t>[9.03, 10.61, 19.28]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[25.1, 25.0, 17.4]</t>
+          <t>[6.3, 6.8, 11.8]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.34761138295511</v>
+        <v>5.094930333163596</v>
       </c>
       <c r="G68" t="n">
-        <v>2.828149646259655</v>
+        <v>4.672546797089217</v>
       </c>
       <c r="H68" t="n">
-        <v>12.5843896360516</v>
+        <v>54.24697579504662</v>
       </c>
     </row>
     <row r="69">
@@ -2890,32 +2890,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[25.16, 14.66, 11.07]</t>
+          <t>[10.11, 18.4, 17.48]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[25.0, 17.4, 12.4]</t>
+          <t>[6.8, 11.8, 10.8]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.760062331650376</v>
+        <v>5.749374781577966</v>
       </c>
       <c r="G69" t="n">
-        <v>1.409139763938446</v>
+        <v>5.530884905517801</v>
       </c>
       <c r="H69" t="n">
-        <v>9.028182122970469</v>
+        <v>55.49694870860365</v>
       </c>
     </row>
     <row r="70">
@@ -2926,32 +2926,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[14.64, 11.06, 5.48]</t>
+          <t>[17.45, 16.58, 15.53]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[17.4, 12.4, 6.6]</t>
+          <t>[11.8, 10.8, 18.1]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.883831756615806</v>
+        <v>4.894874100268106</v>
       </c>
       <c r="G70" t="n">
-        <v>1.737874934214112</v>
+        <v>4.664600085603561</v>
       </c>
       <c r="H70" t="n">
-        <v>14.52464555268898</v>
+        <v>38.51665765621877</v>
       </c>
     </row>
     <row r="71">
@@ -2962,32 +2962,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[11.38, 5.65, 0.2]</t>
+          <t>[15.63, 14.66, 21.1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[12.4, 6.6, 0.2]</t>
+          <t>[10.8, 18.1, 21.4]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.8020441827380979</v>
+        <v>3.427594746242289</v>
       </c>
       <c r="G71" t="n">
-        <v>0.6558905264399228</v>
+        <v>2.858012736910448</v>
       </c>
       <c r="H71" t="n">
-        <v>8.235922933985748</v>
+        <v>21.71343692472197</v>
       </c>
     </row>
     <row r="72">
@@ -2998,32 +2998,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[3607.11, 3967.61, 4857.76]</t>
+          <t>[5683.63, 4313.67, 4590.36]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[3430.5, 3968.2, 4638.7]</t>
+          <t>[6371.8, 5602.1, 5910.7]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>162.460754568093</v>
+        <v>1136.797635381208</v>
       </c>
       <c r="G72" t="n">
-        <v>132.0877365544925</v>
+        <v>1098.980462554551</v>
       </c>
       <c r="H72" t="n">
-        <v>3.295207190713689</v>
+        <v>18.71248313559413</v>
       </c>
     </row>
     <row r="73">
@@ -3034,32 +3034,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[3775.14, 4625.91, 6495.81]</t>
+          <t>[4829.52, 5132.15, 4274.66]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[3968.2, 4638.7, 6160.3]</t>
+          <t>[5602.1, 5910.7, 5144.2]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>223.6106618904684</v>
+        <v>808.1071348439325</v>
       </c>
       <c r="G73" t="n">
-        <v>180.4549958903502</v>
+        <v>806.8882083035978</v>
       </c>
       <c r="H73" t="n">
-        <v>3.529102746813198</v>
+        <v>14.62199679908828</v>
       </c>
     </row>
     <row r="74">
@@ -3070,32 +3070,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[4858.54, 6817.27, 8267.28]</t>
+          <t>[5942.29, 4940.85, 5730.2]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[4638.7, 6160.3, 7165.8]</t>
+          <t>[5910.7, 5144.2, 5378.8]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>751.2654375305195</v>
+        <v>235.1113466520879</v>
       </c>
       <c r="G74" t="n">
-        <v>659.4302790343305</v>
+        <v>195.4473872159297</v>
       </c>
       <c r="H74" t="n">
-        <v>10.25839872491298</v>
+        <v>3.673514978722098</v>
       </c>
     </row>
     <row r="75">
@@ -3106,32 +3106,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[6513.19, 7904.57, 8302.69]</t>
+          <t>[4914.86, 5700.42, 4630.88]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[6160.3, 7165.8, 8386.7]</t>
+          <t>[5144.2, 5378.8, 4112.0]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>475.1746356270476</v>
+        <v>376.5058424102742</v>
       </c>
       <c r="G75" t="n">
-        <v>391.8910233694317</v>
+        <v>356.6125576217661</v>
       </c>
       <c r="H75" t="n">
-        <v>5.679956083005159</v>
+        <v>7.685417306893687</v>
       </c>
     </row>
     <row r="76">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[7482.95, 7866.97, 6591.47]</t>
+          <t>[5963.28, 4841.8, 5349.73]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[7165.8, 8386.7, 7373.9]</t>
+          <t>[5378.8, 4112.0, 4463.5]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>572.3894128618159</v>
+        <v>743.780211794932</v>
       </c>
       <c r="G76" t="n">
-        <v>539.7669063877796</v>
+        <v>733.5033166743797</v>
       </c>
       <c r="H76" t="n">
-        <v>7.07788068512872</v>
+        <v>16.15648439786988</v>
       </c>
     </row>
     <row r="77">
@@ -3178,32 +3178,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[7539.04, 6320.59, 4881.58]</t>
+          <t>[4373.03, 4838.19, 5863.51]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[8386.7, 7373.9, 6371.8]</t>
+          <t>[4112.0, 4463.5, 5183.2]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1161.715232430027</v>
+        <v>473.058760240613</v>
       </c>
       <c r="G77" t="n">
-        <v>1130.39665105785</v>
+        <v>438.6777229969527</v>
       </c>
       <c r="H77" t="n">
-        <v>15.92641288577279</v>
+        <v>9.289299735824507</v>
       </c>
     </row>
     <row r="78">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[7020.58, 5414.12, 4111.7]</t>
+          <t>[4553.01, 5522.34, 7664.25]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[7373.9, 6371.8, 5602.1]</t>
+          <t>[4463.5, 5183.2, 6926.2]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1042.95921299263</v>
+        <v>471.7872719289249</v>
       </c>
       <c r="G78" t="n">
-        <v>933.8008616089182</v>
+        <v>388.9011138890907</v>
       </c>
       <c r="H78" t="n">
-        <v>15.47527859419809</v>
+        <v>6.401469703721354</v>
       </c>
     </row>
     <row r="79">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[5683.63, 4313.67, 4590.36]</t>
+          <t>[5414.94, 7517.05, 9039.2]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[6371.8, 5602.1, 5910.7]</t>
+          <t>[5183.2, 6926.2, 7755.3]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1136.797635381208</v>
+        <v>826.8810559232437</v>
       </c>
       <c r="G79" t="n">
-        <v>1098.980462554551</v>
+        <v>702.1625179870289</v>
       </c>
       <c r="H79" t="n">
-        <v>18.71248313559413</v>
+        <v>9.852251862296592</v>
       </c>
     </row>
     <row r="80">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[4829.52, 5132.15, 4274.66]</t>
+          <t>[7199.69, 8663.03, 9251.02]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[5602.1, 5910.7, 5144.2]</t>
+          <t>[6926.2, 7755.3, 8152.1]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>808.1071348439325</v>
+        <v>837.9363127770067</v>
       </c>
       <c r="G80" t="n">
-        <v>806.8882083035978</v>
+        <v>760.0500996885488</v>
       </c>
       <c r="H80" t="n">
-        <v>14.62199679908828</v>
+        <v>9.711204492570912</v>
       </c>
     </row>
     <row r="81">
@@ -3322,32 +3322,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[5942.29, 4940.85, 5730.2]</t>
+          <t>[8338.32, 8908.93, 7504.96]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[5910.7, 5144.2, 5378.8]</t>
+          <t>[7755.3, 8152.1, 6931.2]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>235.1113466520879</v>
+        <v>643.4049504592233</v>
       </c>
       <c r="G81" t="n">
-        <v>195.4473872159297</v>
+        <v>637.8715462423939</v>
       </c>
       <c r="H81" t="n">
-        <v>3.673514978722098</v>
+        <v>8.359853510096681</v>
       </c>
     </row>
     <row r="82">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[9623.61, 10761.29, 12218.23]</t>
+          <t>[25225.49, 24927.35, 15678.36]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[11727.3, 11830.5, 12628.7]</t>
+          <t>[24907.0, 24341.0, 15457.5]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1382.896114549383</v>
+        <v>405.7998136836273</v>
       </c>
       <c r="G82" t="n">
-        <v>1194.456953796384</v>
+        <v>375.2331940735791</v>
       </c>
       <c r="H82" t="n">
-        <v>10.07548070725441</v>
+        <v>1.705476195478307</v>
       </c>
     </row>
     <row r="83">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[12062.43, 13594.02, 21416.9]</t>
+          <t>[24755.6, 15570.25, 14725.55]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[11830.5, 12628.7, 19916.2]</t>
+          <t>[24341.0, 15457.5, 14452.4]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1038.866530759032</v>
+        <v>293.9450761311535</v>
       </c>
       <c r="G83" t="n">
-        <v>899.314928954603</v>
+        <v>266.830278527125</v>
       </c>
       <c r="H83" t="n">
-        <v>5.713108248754184</v>
+        <v>1.440887734621632</v>
       </c>
     </row>
     <row r="84">
@@ -3430,32 +3430,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[13434.1, 21168.09, 23278.43]</t>
+          <t>[15427.71, 14590.76, 17697.84]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[12628.7, 19916.2, 21610.9]</t>
+          <t>[15457.5, 14452.4, 18270.8]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1290.551203531243</v>
+        <v>340.7410117630519</v>
       </c>
       <c r="G84" t="n">
-        <v>1241.608642834559</v>
+        <v>247.0356271374324</v>
       </c>
       <c r="H84" t="n">
-        <v>6.793171771334704</v>
+        <v>1.428661268472562</v>
       </c>
     </row>
     <row r="85">
@@ -3466,32 +3466,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[20441.27, 22498.83, 30408.36]</t>
+          <t>[14606.1, 17716.47, 10619.42]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[19916.2, 21610.9, 28942.5]</t>
+          <t>[14452.4, 18270.8, 11870.5]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1034.868443935778</v>
+        <v>795.003922882895</v>
       </c>
       <c r="G85" t="n">
-        <v>959.6193870157513</v>
+        <v>653.0335963518264</v>
       </c>
       <c r="H85" t="n">
-        <v>3.936611798468579</v>
+        <v>4.878933844033717</v>
       </c>
     </row>
     <row r="86">
@@ -3502,32 +3502,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[22179.74, 29980.59, 22803.63]</t>
+          <t>[17616.03, 10558.04, 10804.04]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[21610.9, 28942.5, 22208.3]</t>
+          <t>[18270.8, 11870.5, 11950.3]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>764.9898289599622</v>
+        <v>1074.740693312708</v>
       </c>
       <c r="G86" t="n">
-        <v>734.0865510447002</v>
+        <v>1037.832712957119</v>
       </c>
       <c r="H86" t="n">
-        <v>2.966527940777337</v>
+        <v>8.077377760409131</v>
       </c>
     </row>
     <row r="87">
@@ -3538,32 +3538,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[29554.94, 22479.15, 25526.0]</t>
+          <t>[10767.71, 11014.47, 12161.69]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[28942.5, 22208.3, 24907.0]</t>
+          <t>[11870.5, 11950.3, 12804.8]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>526.4970445184382</v>
+        <v>913.8770938890946</v>
       </c>
       <c r="G87" t="n">
-        <v>500.7618023984505</v>
+        <v>893.9094543275393</v>
       </c>
       <c r="H87" t="n">
-        <v>1.940292182751146</v>
+        <v>7.381197154097167</v>
       </c>
     </row>
     <row r="88">
@@ -3574,32 +3574,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[22223.57, 25234.93, 24936.67]</t>
+          <t>[11630.59, 12839.92, 20485.14]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[22208.3, 24907.0, 24341.0]</t>
+          <t>[11950.3, 12804.8, 20325.3]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>392.6790290832951</v>
+        <v>207.3610925937751</v>
       </c>
       <c r="G88" t="n">
-        <v>312.9538188337113</v>
+        <v>171.5566318606949</v>
       </c>
       <c r="H88" t="n">
-        <v>1.277509078913316</v>
+        <v>1.245332397798033</v>
       </c>
     </row>
     <row r="89">
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[25225.49, 24927.35, 15678.36]</t>
+          <t>[13039.65, 20793.5, 22862.06]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[24907.0, 24341.0, 15457.5]</t>
+          <t>[12804.8, 20325.3, 21966.6]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>405.7998136836273</v>
+        <v>598.9486078691618</v>
       </c>
       <c r="G89" t="n">
-        <v>375.2331940735791</v>
+        <v>532.8364745664621</v>
       </c>
       <c r="H89" t="n">
-        <v>1.705476195478307</v>
+        <v>2.738019192117496</v>
       </c>
     </row>
     <row r="90">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[24755.6, 15570.25, 14725.55]</t>
+          <t>[20584.95, 22635.29, 30642.61]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[24341.0, 15457.5, 14452.4]</t>
+          <t>[20325.3, 21966.6, 29428.1]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>293.9450761311535</v>
+        <v>814.3682743113092</v>
       </c>
       <c r="G90" t="n">
-        <v>266.830278527125</v>
+        <v>714.2812200720122</v>
       </c>
       <c r="H90" t="n">
-        <v>1.440887734621632</v>
+        <v>2.816203654251725</v>
       </c>
     </row>
     <row r="91">
@@ -3682,32 +3682,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[15427.71, 14590.76, 17697.84]</t>
+          <t>[22477.83, 30430.18, 23327.31]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[15457.5, 14452.4, 18270.8]</t>
+          <t>[21966.6, 29428.1, 22638.4]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>340.7410117630519</v>
+        <v>761.6061248517324</v>
       </c>
       <c r="G91" t="n">
-        <v>247.0356271374324</v>
+        <v>734.0763725191173</v>
       </c>
       <c r="H91" t="n">
-        <v>1.428661268472562</v>
+        <v>2.925208866937335</v>
       </c>
     </row>
     <row r="92">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[3608.37, 5970.96, 9042.67]</t>
+          <t>[23413.59, 22459.35, 13258.12]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[3219.2, 6442.5, 8738.0]</t>
+          <t>[20199.8, 19579.4, 11174.1]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>394.3901258532021</v>
+        <v>2766.810677355764</v>
       </c>
       <c r="G92" t="n">
-        <v>388.4611040927636</v>
+        <v>2725.921739606432</v>
       </c>
       <c r="H92" t="n">
-        <v>7.631688476188359</v>
+        <v>16.42319211958283</v>
       </c>
     </row>
     <row r="93">
@@ -3754,32 +3754,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[5875.28, 8899.58, 18515.59]</t>
+          <t>[22076.09, 13033.78, 10413.39]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[6442.5, 8738.0, 18832.4]</t>
+          <t>[19579.4, 11174.1, 9415.9]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>386.5289030841691</v>
+        <v>1887.400520420762</v>
       </c>
       <c r="G93" t="n">
-        <v>348.5370330174519</v>
+        <v>1784.619478998466</v>
       </c>
       <c r="H93" t="n">
-        <v>4.111928432585793</v>
+        <v>13.32935748330251</v>
       </c>
     </row>
     <row r="94">
@@ -3790,32 +3790,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[9016.74, 18756.6, 35435.91]</t>
+          <t>[12824.59, 10247.26, 9815.38]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[8738.0, 18832.4, 34459.1]</t>
+          <t>[11174.1, 9415.9, 9712.4]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>588.1056401805058</v>
+        <v>1068.624835701213</v>
       </c>
       <c r="G94" t="n">
-        <v>443.7818415352043</v>
+        <v>861.6090758468703</v>
       </c>
       <c r="H94" t="n">
-        <v>2.142367158430948</v>
+        <v>8.220086404480643</v>
       </c>
     </row>
     <row r="95">
@@ -3826,32 +3826,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[18687.09, 35304.65, 38753.11]</t>
+          <t>[10032.12, 9611.67, 3336.91]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[18832.4, 34459.1, 39307.0]</t>
+          <t>[9415.9, 9712.4, 3211.2]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>589.5958573130511</v>
+        <v>367.7333436759909</v>
       </c>
       <c r="G95" t="n">
-        <v>514.9176159139473</v>
+        <v>280.8896383464627</v>
       </c>
       <c r="H95" t="n">
-        <v>1.544840375636505</v>
+        <v>3.832136610853196</v>
       </c>
     </row>
     <row r="96">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[35338.11, 38788.48, 29057.75]</t>
+          <t>[9506.99, 3301.12, 5571.13]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[34459.1, 39307.0, 27028.6]</t>
+          <t>[9712.4, 3211.2, 6609.1]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1311.358712537368</v>
+        <v>613.0981457321786</v>
       </c>
       <c r="G96" t="n">
-        <v>1142.226597336617</v>
+        <v>444.4366079866889</v>
       </c>
       <c r="H96" t="n">
-        <v>3.792485434411509</v>
+        <v>6.873492303049937</v>
       </c>
     </row>
     <row r="97">
@@ -3898,32 +3898,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[38674.84, 28978.88, 23557.08]</t>
+          <t>[3313.07, 5590.43, 8378.46]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[39307.0, 27028.6, 20199.8]</t>
+          <t>[3211.2, 6609.1, 9067.3]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2271.164248636909</v>
+        <v>712.4075587431405</v>
       </c>
       <c r="G97" t="n">
-        <v>1979.906946643848</v>
+        <v>603.1290996484527</v>
       </c>
       <c r="H97" t="n">
-        <v>8.48141652360375</v>
+        <v>8.727543599606298</v>
       </c>
     </row>
     <row r="98">
@@ -3934,32 +3934,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[29028.25, 23594.37, 22630.22]</t>
+          <t>[5563.34, 8338.61, 17418.91]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[27028.6, 20199.8, 19579.4]</t>
+          <t>[6609.1, 9067.3, 19342.5]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2876.872196348069</v>
+        <v>1332.264674148401</v>
       </c>
       <c r="G98" t="n">
-        <v>2815.012122169798</v>
+        <v>1232.678781171387</v>
       </c>
       <c r="H98" t="n">
-        <v>13.26166877889801</v>
+        <v>11.2681168348143</v>
       </c>
     </row>
     <row r="99">
@@ -3970,32 +3970,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[23413.59, 22459.35, 13258.12]</t>
+          <t>[8547.56, 17851.48, 33632.52]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[20199.8, 19579.4, 11174.1]</t>
+          <t>[9067.3, 19342.5, 35421.8]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2766.810677355764</v>
+        <v>1377.774115779853</v>
       </c>
       <c r="G99" t="n">
-        <v>2725.921739606432</v>
+        <v>1266.678382503852</v>
       </c>
       <c r="H99" t="n">
-        <v>16.42319211958283</v>
+        <v>6.163951505913446</v>
       </c>
     </row>
     <row r="100">
@@ -4006,32 +4006,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[22076.09, 13033.78, 10413.39]</t>
+          <t>[17981.55, 33875.89, 37336.53]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[19579.4, 11174.1, 9415.9]</t>
+          <t>[19342.5, 35421.8, 40245.9]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1887.400520420762</v>
+        <v>2058.026761235216</v>
       </c>
       <c r="G100" t="n">
-        <v>1784.619478998466</v>
+        <v>1938.741039122139</v>
       </c>
       <c r="H100" t="n">
-        <v>13.32935748330251</v>
+        <v>6.209770511012602</v>
       </c>
     </row>
     <row r="101">
@@ -4042,32 +4042,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[12824.59, 10247.26, 9815.38]</t>
+          <t>[34172.38, 37657.64, 27978.61]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[11174.1, 9415.9, 9712.4]</t>
+          <t>[35421.8, 40245.9, 28134.5]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1068.624835701213</v>
+        <v>1661.771539211181</v>
       </c>
       <c r="G101" t="n">
-        <v>861.6090758468703</v>
+        <v>1331.191173173297</v>
       </c>
       <c r="H101" t="n">
-        <v>8.220086404480643</v>
+        <v>3.50415908523907</v>
       </c>
     </row>
     <row r="102">
@@ -4078,32 +4078,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[4374.38, 7010.42, 16833.36]</t>
+          <t>[19280.4, 19913.88, 13533.84]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[4432.0, 7097.0, 16260.8]</t>
+          <t>[18272.4, 23386.7, 13690.0]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>335.975695851114</v>
+        <v>2089.731472594837</v>
       </c>
       <c r="G102" t="n">
-        <v>238.9201769135143</v>
+        <v>1545.65983007362</v>
       </c>
       <c r="H102" t="n">
-        <v>2.013719575806682</v>
+        <v>7.168915780800335</v>
       </c>
     </row>
     <row r="103">
@@ -4114,32 +4114,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[7067.16, 16966.74, 16614.76]</t>
+          <t>[19271.58, 13101.12, 11563.45]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[7097.0, 16260.8, 16243.8]</t>
+          <t>[23386.7, 13690.0, 12115.0]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>460.743908119849</v>
+        <v>2421.102912710156</v>
       </c>
       <c r="G103" t="n">
-        <v>368.9145918412926</v>
+        <v>1751.850409023172</v>
       </c>
       <c r="H103" t="n">
-        <v>2.348516622812946</v>
+        <v>8.81671296198785</v>
       </c>
     </row>
     <row r="104">
@@ -4150,32 +4150,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[17010.61, 16657.21, 26723.54]</t>
+          <t>[14734.47, 12990.74, 21188.88]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[16260.8, 16243.8, 24404.2]</t>
+          <t>[13690.0, 12115.0, 20918.7]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1427.406725655154</v>
+        <v>802.2525534462807</v>
       </c>
       <c r="G104" t="n">
-        <v>1160.851563290037</v>
+        <v>730.129068281316</v>
       </c>
       <c r="H104" t="n">
-        <v>5.553332542644862</v>
+        <v>5.383180308319527</v>
       </c>
     </row>
     <row r="105">
@@ -4186,32 +4186,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[16203.19, 26001.4, 31066.96]</t>
+          <t>[12424.49, 20273.8, 4531.98]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[16243.8, 24404.2, 31986.3]</t>
+          <t>[12115.0, 20918.7, 4413.5]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1064.246626062547</v>
+        <v>418.6162216494355</v>
       </c>
       <c r="G105" t="n">
-        <v>852.3820479116997</v>
+        <v>357.623804635321</v>
       </c>
       <c r="H105" t="n">
-        <v>3.222981061276537</v>
+        <v>2.773992610399048</v>
       </c>
     </row>
     <row r="106">
@@ -4222,32 +4222,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[26041.31, 31115.28, 21898.27]</t>
+          <t>[19968.69, 4464.46, 7153.64]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[24404.2, 31986.3, 22235.4]</t>
+          <t>[20918.7, 4413.5, 7045.2]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1088.188208745246</v>
+        <v>552.8314746763882</v>
       </c>
       <c r="G106" t="n">
-        <v>948.4207624505483</v>
+        <v>369.8020339845986</v>
       </c>
       <c r="H106" t="n">
-        <v>3.649204045287265</v>
+        <v>2.411743823546417</v>
       </c>
     </row>
     <row r="107">
@@ -4258,32 +4258,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[29900.11, 21049.3, 18355.38]</t>
+          <t>[4590.79, 7354.35, 17567.84]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[31986.3, 22235.4, 18272.4]</t>
+          <t>[4413.5, 7045.2, 16438.5]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1386.352651311028</v>
+        <v>683.7200985568301</v>
       </c>
       <c r="G107" t="n">
-        <v>1118.425659479064</v>
+        <v>538.5941333519198</v>
       </c>
       <c r="H107" t="n">
-        <v>4.103527307095596</v>
+        <v>5.091729714752261</v>
       </c>
     </row>
     <row r="108">
@@ -4294,32 +4294,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[21938.0, 19122.22, 19751.98]</t>
+          <t>[7181.76, 17158.85, 16834.23]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[22235.4, 18272.4, 23386.7]</t>
+          <t>[7045.2, 16438.5, 16593.3]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2161.929267477533</v>
+        <v>445.5734807492308</v>
       </c>
       <c r="G108" t="n">
-        <v>1593.977645600489</v>
+        <v>365.9487230910806</v>
       </c>
       <c r="H108" t="n">
-        <v>7.1767125998503</v>
+        <v>2.590816085923168</v>
       </c>
     </row>
     <row r="109">
@@ -4330,32 +4330,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[19280.4, 19913.88, 13533.84]</t>
+          <t>[16961.75, 16642.15, 26524.68]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[18272.4, 23386.7, 13690.0]</t>
+          <t>[16438.5, 16593.3, 25008.4]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2089.731472594837</v>
+        <v>926.5123228302713</v>
       </c>
       <c r="G109" t="n">
-        <v>1545.65983007362</v>
+        <v>696.1262809505448</v>
       </c>
       <c r="H109" t="n">
-        <v>7.168915780800335</v>
+        <v>3.18018425504459</v>
       </c>
     </row>
     <row r="110">
@@ -4366,32 +4366,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[19271.58, 13101.12, 11563.45]</t>
+          <t>[16331.91, 26032.95, 31391.57]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[23386.7, 13690.0, 12115.0]</t>
+          <t>[16593.3, 25008.4, 33051.3]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2421.102912710156</v>
+        <v>1136.183759820791</v>
       </c>
       <c r="G110" t="n">
-        <v>1751.850409023172</v>
+        <v>981.8912143461488</v>
       </c>
       <c r="H110" t="n">
-        <v>8.81671296198785</v>
+        <v>3.564596614977948</v>
       </c>
     </row>
     <row r="111">
@@ -4402,32 +4402,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[14734.47, 12990.74, 21188.88]</t>
+          <t>[26283.93, 31690.94, 22273.29]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[13690.0, 12115.0, 20918.7]</t>
+          <t>[25008.4, 33051.3, 22114.3]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>802.2525534462807</v>
+        <v>1080.560209474451</v>
       </c>
       <c r="G111" t="n">
-        <v>730.129068281316</v>
+        <v>931.6262894371612</v>
       </c>
       <c r="H111" t="n">
-        <v>5.383180308319527</v>
+        <v>3.311749912689325</v>
       </c>
     </row>
     <row r="112">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[10071.57, 12909.89, 13575.77]</t>
+          <t>[11808.03, 11395.77, 9783.39]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[11065.4, 13251.6, 13867.7]</t>
+          <t>[13406.8, 12774.7, 11421.4]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>629.7317845085357</v>
+        <v>1542.790349675464</v>
       </c>
       <c r="G112" t="n">
-        <v>542.4898553419571</v>
+        <v>1538.57179921691</v>
       </c>
       <c r="H112" t="n">
-        <v>4.555052043665754</v>
+        <v>12.35364081372567</v>
       </c>
     </row>
     <row r="113">
@@ -4474,32 +4474,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[13424.15, 14110.55, 26362.61]</t>
+          <t>[12013.38, 10310.56, 6503.21]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[13251.6, 13867.7, 22759.5]</t>
+          <t>[12774.7, 11421.4, 8236.4]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2087.352911870622</v>
+        <v>1267.216263834946</v>
       </c>
       <c r="G113" t="n">
-        <v>1339.501940922941</v>
+        <v>1201.781734497912</v>
       </c>
       <c r="H113" t="n">
-        <v>6.294837784999885</v>
+        <v>12.24285177025914</v>
       </c>
     </row>
     <row r="114">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[14034.64, 26221.28, 27634.69]</t>
+          <t>[10577.14, 6669.48, 9799.97]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[13867.7, 22759.5, 22176.5]</t>
+          <t>[11421.4, 8236.4, 9839.8]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3732.901260310255</v>
+        <v>1027.878812370318</v>
       </c>
       <c r="G114" t="n">
-        <v>3028.970448754676</v>
+        <v>817.0022288997085</v>
       </c>
       <c r="H114" t="n">
-        <v>13.67552046818632</v>
+        <v>8.940336624796833</v>
       </c>
     </row>
     <row r="115">
@@ -4546,32 +4546,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[26095.1, 27499.0, 50514.99]</t>
+          <t>[6886.69, 10116.16, 10225.8]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[22759.5, 22176.5, 43579.6]</t>
+          <t>[8236.4, 9839.8, 12296.7]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>5402.312495898691</v>
+        <v>1436.050176965031</v>
       </c>
       <c r="G115" t="n">
-        <v>5197.832551490069</v>
+        <v>1232.323349357433</v>
       </c>
       <c r="H115" t="n">
-        <v>18.19027491119669</v>
+        <v>12.0122815795965</v>
       </c>
     </row>
     <row r="116">
@@ -4582,32 +4582,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[25992.12, 47778.1, 25757.84]</t>
+          <t>[10912.78, 11022.94, 14024.58]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[22176.5, 43579.6, 23723.6]</t>
+          <t>[9839.8, 12296.7, 14608.5]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3479.678773070198</v>
+        <v>1018.937319959707</v>
       </c>
       <c r="G116" t="n">
-        <v>3349.452897933254</v>
+        <v>976.8846307729078</v>
       </c>
       <c r="H116" t="n">
-        <v>11.80484507868272</v>
+        <v>8.420036209901758</v>
       </c>
     </row>
     <row r="117">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[44711.18, 24119.28, 11964.39]</t>
+          <t>[10550.92, 13428.73, 14109.13]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[43579.6, 23723.6, 13406.8]</t>
+          <t>[12296.7, 14608.5, 15571.1]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1082.833020135966</v>
+        <v>1480.6489777938</v>
       </c>
       <c r="G117" t="n">
-        <v>989.8903742086495</v>
+        <v>1462.506857743589</v>
       </c>
       <c r="H117" t="n">
-        <v>5.00774712701392</v>
+        <v>10.55401824295214</v>
       </c>
     </row>
     <row r="118">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[23859.79, 11836.24, 11422.99]</t>
+          <t>[14323.0, 15040.63, 27722.48]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[23723.6, 13406.8, 12774.7]</t>
+          <t>[14608.5, 15571.1, 25665.2]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1198.93204309657</v>
+        <v>1237.645957649692</v>
       </c>
       <c r="G118" t="n">
-        <v>1019.486127558332</v>
+        <v>957.7498380544948</v>
       </c>
       <c r="H118" t="n">
-        <v>7.623283663717167</v>
+        <v>4.458979562696469</v>
       </c>
     </row>
     <row r="119">
@@ -4690,32 +4690,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[11808.03, 11395.77, 9783.39]</t>
+          <t>[15166.64, 27953.53, 29208.4]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[13406.8, 12774.7, 11421.4]</t>
+          <t>[15571.1, 25665.2, 24862.8]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1542.790349675464</v>
+        <v>2845.131322957284</v>
       </c>
       <c r="G119" t="n">
-        <v>1538.57179921691</v>
+        <v>2346.133066260212</v>
       </c>
       <c r="H119" t="n">
-        <v>12.35364081372567</v>
+        <v>9.663983591359955</v>
       </c>
     </row>
     <row r="120">
@@ -4726,32 +4726,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[12013.38, 10310.56, 6503.21]</t>
+          <t>[28266.65, 29530.48, 54570.2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[12774.7, 11421.4, 8236.4]</t>
+          <t>[25665.2, 24862.8, 48355.4]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1267.216263834946</v>
+        <v>4732.106254084654</v>
       </c>
       <c r="G120" t="n">
-        <v>1201.781734497912</v>
+        <v>4494.643327030451</v>
       </c>
       <c r="H120" t="n">
-        <v>12.24285177025914</v>
+        <v>13.92073222468649</v>
       </c>
     </row>
     <row r="121">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[10577.14, 6669.48, 9799.97]</t>
+          <t>[28363.11, 52426.8, 28268.65]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[11421.4, 8236.4, 9839.8]</t>
+          <t>[24862.8, 48355.4, 24434.4]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1027.878812370318</v>
+        <v>3809.194656500112</v>
       </c>
       <c r="G121" t="n">
-        <v>817.0022288997085</v>
+        <v>3801.984553878192</v>
       </c>
       <c r="H121" t="n">
-        <v>8.940336624796833</v>
+        <v>12.73008097393145</v>
       </c>
     </row>
     <row r="122">
@@ -4798,32 +4798,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[8259.28, 8212.64, 9397.06]</t>
+          <t>[4454.19, 4445.43, 4249.65]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[2911.0, 2981.0, 3217.2]</t>
+          <t>[4363.4, 4359.7, 4199.9]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>5602.525185688063</v>
+        <v>77.60662656687323</v>
       </c>
       <c r="G122" t="n">
-        <v>5586.594612840938</v>
+        <v>75.4249854811366</v>
       </c>
       <c r="H122" t="n">
-        <v>183.7714440598467</v>
+        <v>1.743934106903241</v>
       </c>
     </row>
     <row r="123">
@@ -4834,32 +4834,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[3942.93, 4960.31, 5594.8]</t>
+          <t>[4395.72, 4202.13, 4399.5]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[2981.0, 3217.2, 3592.6]</t>
+          <t>[4359.7, 4199.9, 4408.5]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1630.191602599225</v>
+        <v>21.47652646690559</v>
       </c>
       <c r="G123" t="n">
-        <v>1569.082870934672</v>
+        <v>15.7513351813274</v>
       </c>
       <c r="H123" t="n">
-        <v>47.39372006251033</v>
+        <v>0.3611804393323724</v>
       </c>
     </row>
     <row r="124">
@@ -4870,32 +4870,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[4300.35, 4882.67, 5354.64]</t>
+          <t>[4183.33, 4379.81, 7835.6]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[3217.2, 3592.6, 3849.6]</t>
+          <t>[4199.9, 4408.5, 5646.6]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1304.177810116061</v>
+        <v>1263.963799810423</v>
       </c>
       <c r="G124" t="n">
-        <v>1292.752999169255</v>
+        <v>744.7542869295181</v>
       </c>
       <c r="H124" t="n">
-        <v>36.22417906693018</v>
+        <v>13.27069576919476</v>
       </c>
     </row>
     <row r="125">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[4215.91, 4618.88, 5161.11]</t>
+          <t>[4389.25, 7852.76, 1836.36]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[3592.6, 3849.6, 4301.2]</t>
+          <t>[4408.5, 5646.6, 3000.2]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>757.1328329637779</v>
+        <v>1440.141088735468</v>
       </c>
       <c r="G125" t="n">
-        <v>750.8326131904123</v>
+        <v>1129.747718361695</v>
       </c>
       <c r="H125" t="n">
-        <v>19.10848755665207</v>
+        <v>26.09974000520818</v>
       </c>
     </row>
     <row r="126">
@@ -4942,32 +4942,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[4199.87, 4684.74, 4708.6]</t>
+          <t>[7871.46, 1840.74, 2201.73]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[3849.6, 4301.2, 4309.9]</t>
+          <t>[5646.6, 3000.2, 3036.2]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>378.0466116163502</v>
+        <v>1526.509313239887</v>
       </c>
       <c r="G126" t="n">
-        <v>377.5050596612766</v>
+        <v>1406.263838817</v>
       </c>
       <c r="H126" t="n">
-        <v>9.088943777232201</v>
+        <v>35.17730512214357</v>
       </c>
     </row>
     <row r="127">
@@ -4978,32 +4978,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[4450.49, 4472.07, 4584.7]</t>
+          <t>[2061.51, 2351.38, 2842.68]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[4301.2, 4309.9, 4363.4]</t>
+          <t>[3000.2, 3036.2, 3195.7]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>180.335142992532</v>
+        <v>701.1300072062812</v>
       </c>
       <c r="G127" t="n">
-        <v>177.5884452505855</v>
+        <v>658.8457229987133</v>
       </c>
       <c r="H127" t="n">
-        <v>4.101826787990873</v>
+        <v>21.62990036517049</v>
       </c>
     </row>
     <row r="128">
@@ -5014,32 +5014,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[4387.16, 4497.79, 4489.01]</t>
+          <t>[2944.51, 3378.47, 3767.48]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[4309.9, 4363.4, 4359.7]</t>
+          <t>[3036.2, 3195.7, 3601.1]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>116.5476364136705</v>
+        <v>152.1996191078499</v>
       </c>
       <c r="G128" t="n">
-        <v>113.6523859052365</v>
+        <v>146.9463525005316</v>
       </c>
       <c r="H128" t="n">
-        <v>2.612839796827333</v>
+        <v>4.453116831884103</v>
       </c>
     </row>
     <row r="129">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[4454.19, 4445.43, 4249.65]</t>
+          <t>[3429.3, 3823.81, 4153.46]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[4363.4, 4359.7, 4199.9]</t>
+          <t>[3195.7, 3601.1, 3887.4]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>77.60662656687323</v>
+        <v>241.4940842087335</v>
       </c>
       <c r="G129" t="n">
-        <v>75.4249854811366</v>
+        <v>240.7908499078217</v>
       </c>
       <c r="H129" t="n">
-        <v>1.743934106903241</v>
+        <v>6.779517192145311</v>
       </c>
     </row>
     <row r="130">
@@ -5086,32 +5086,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[4395.72, 4202.13, 4399.5]</t>
+          <t>[3694.09, 4014.22, 4440.23]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[4359.7, 4199.9, 4408.5]</t>
+          <t>[3601.1, 3887.4, 4754.3]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>21.47652646690559</v>
+        <v>202.7911904291544</v>
       </c>
       <c r="G130" t="n">
-        <v>15.7513351813274</v>
+        <v>177.9611703323726</v>
       </c>
       <c r="H130" t="n">
-        <v>0.3611804393323724</v>
+        <v>4.150229693102196</v>
       </c>
     </row>
     <row r="131">
@@ -5122,32 +5122,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[4183.33, 4379.81, 7835.6]</t>
+          <t>[3964.48, 4386.05, 4402.01]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[4199.9, 4408.5, 5646.6]</t>
+          <t>[3887.4, 4754.3, 4682.9]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1263.963799810423</v>
+        <v>271.0773798225608</v>
       </c>
       <c r="G131" t="n">
-        <v>744.7542869295181</v>
+        <v>242.0719692769679</v>
       </c>
       <c r="H131" t="n">
-        <v>13.27069576919476</v>
+        <v>5.24217804216651</v>
       </c>
     </row>
     <row r="132">
@@ -5158,17 +5158,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[-0.48, -0.43, -0.28]</t>
+          <t>[-0.21, -0.23, -0.38]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.4058522786126702</v>
+        <v>0.283214447362168</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3970051492485811</v>
+        <v>0.2731512778257015</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5196,17 +5196,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[0.09, 0.35, 0.71]</t>
+          <t>[-0.04, -0.22, -0.42]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.4614691954927509</v>
+        <v>0.2768589428184389</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3841050252568794</v>
+        <v>0.2297989182953317</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5234,17 +5234,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[0.25, 0.58, 5.13]</t>
+          <t>[-0.19, -0.4, -0.34]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2.985481948509396</v>
+        <v>0.3207689265786985</v>
       </c>
       <c r="G134" t="n">
-        <v>1.98541203719485</v>
+        <v>0.3087791467403371</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5272,17 +5272,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[0.28, 3.97, 1.43]</t>
+          <t>[-0.26, -0.19, -0.55]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2.439564474445169</v>
+        <v>0.3687489588958501</v>
       </c>
       <c r="G135" t="n">
-        <v>1.889942189279028</v>
+        <v>0.3346094419557769</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5310,17 +5310,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[2.92, 0.92, 1.21]</t>
+          <t>[0.08, -0.4, -0.34]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1.901789911381194</v>
+        <v>0.3071396191568289</v>
       </c>
       <c r="G136" t="n">
-        <v>1.684503300445964</v>
+        <v>0.2737693929674664</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[-0.49, -0.41, -0.53]</t>
+          <t>[-0.44, -0.39, -0.25]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.4812291601511686</v>
+        <v>0.3697087981304413</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4785026432069772</v>
+        <v>0.3609690770961304</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -5386,17 +5386,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[0.14, -0.1, -0.13]</t>
+          <t>[0.07, 0.3, 0.61]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.1260603507121193</v>
+        <v>0.3969592615337098</v>
       </c>
       <c r="G138" t="n">
-        <v>0.1250977315528176</v>
+        <v>0.3295382935656363</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -5424,17 +5424,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[-0.21, -0.23, -0.38]</t>
+          <t>[0.22, 0.51, 4.12]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.283214447362168</v>
+        <v>2.398839507637885</v>
       </c>
       <c r="G139" t="n">
-        <v>0.2731512778257015</v>
+        <v>1.6151325789916</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -5462,17 +5462,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[-0.04, -0.22, -0.42]</t>
+          <t>[0.25, 3.24, 1.22]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.2768589428184389</v>
+        <v>2.004412729622277</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2297989182953317</v>
+        <v>1.570229237554247</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -5500,17 +5500,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[-0.19, -0.4, -0.34]</t>
+          <t>[2.43, 0.8, 1.05]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.3207689265786985</v>
+        <v>1.594856570062236</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3087791467403371</v>
+        <v>1.425122201533445</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -5538,32 +5538,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[41873.2, 38120.49, 36726.04]</t>
+          <t>[33113.36, 30772.2, 24597.41]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[39750.2, 34238.1, 32329.0]</t>
+          <t>[32329.0, 30870.5, 24860.8]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3601.573434742973</v>
+        <v>481.0614309283366</v>
       </c>
       <c r="G142" t="n">
-        <v>3467.473951969563</v>
+        <v>382.0175018364607</v>
       </c>
       <c r="H142" t="n">
-        <v>10.09371070601681</v>
+        <v>1.268025852756633</v>
       </c>
     </row>
     <row r="143">
@@ -5574,32 +5574,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[36269.61, 35020.5, 32490.95]</t>
+          <t>[30059.17, 24045.31, 21072.04]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[34238.1, 32329.0, 30870.5]</t>
+          <t>[30870.5, 24860.8, 19961.8]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2160.018707762948</v>
+        <v>923.0228492833846</v>
       </c>
       <c r="G143" t="n">
-        <v>2114.484470123409</v>
+        <v>912.3537421122128</v>
       </c>
       <c r="H143" t="n">
-        <v>6.502662046612875</v>
+        <v>3.823406688408738</v>
       </c>
     </row>
     <row r="144">
@@ -5610,32 +5610,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[33113.36, 30772.2, 24597.41]</t>
+          <t>[24674.37, 21605.96, 18900.87]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[32329.0, 30870.5, 24860.8]</t>
+          <t>[24860.8, 19961.8, 16735.6]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>481.0614309283366</v>
+        <v>1573.361003685469</v>
       </c>
       <c r="G144" t="n">
-        <v>382.0175018364607</v>
+        <v>1331.953359223131</v>
       </c>
       <c r="H144" t="n">
-        <v>1.268025852756633</v>
+        <v>7.308175587960698</v>
       </c>
     </row>
     <row r="145">
@@ -5646,32 +5646,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[30059.17, 24045.31, 21072.04]</t>
+          <t>[21769.07, 19039.71, 7596.19]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[30870.5, 24860.8, 19961.8]</t>
+          <t>[19961.8, 16735.6, 9509.8]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>923.0228492833846</v>
+        <v>2019.657919841754</v>
       </c>
       <c r="G145" t="n">
-        <v>912.3537421122128</v>
+        <v>2008.330512679771</v>
       </c>
       <c r="H145" t="n">
-        <v>3.823406688408738</v>
+        <v>14.3146239763723</v>
       </c>
     </row>
     <row r="146">
@@ -5682,1472 +5682,2012 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[24674.37, 21605.96, 18900.87]</t>
+          <t>[17506.11, 7002.3, 9779.25]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[24860.8, 19961.8, 16735.6]</t>
+          <t>[16735.6, 9509.8, 12638.2]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1573.361003685469</v>
+        <v>2240.154687520074</v>
       </c>
       <c r="G146" t="n">
-        <v>1331.953359223131</v>
+        <v>2045.655697327775</v>
       </c>
       <c r="H146" t="n">
-        <v>7.308175587960698</v>
+        <v>17.86437388704609</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[26605.83, 21867.91, 22625.55]</t>
+          <t>[6705.94, 9377.06, 16255.19]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[25872.9, 21118.6, 20792.5]</t>
+          <t>[9509.8, 12638.2, 20932.4]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1219.112820520239</v>
+        <v>3668.46938724411</v>
       </c>
       <c r="G147" t="n">
-        <v>1105.094751775787</v>
+        <v>3580.738753182186</v>
       </c>
       <c r="H147" t="n">
-        <v>5.065602647421366</v>
+        <v>25.87737949620628</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[21289.98, 22051.89, 26672.77]</t>
+          <t>[13138.92, 22503.24, 28404.35]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[21118.6, 20792.5, 25258.8]</t>
+          <t>[12638.2, 20932.4, 26104.5]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1097.689414890465</v>
+        <v>1633.767350545486</v>
       </c>
       <c r="G148" t="n">
-        <v>948.2493403822773</v>
+        <v>1457.138563994001</v>
       </c>
       <c r="H148" t="n">
-        <v>4.155473877081562</v>
+        <v>6.758832942388087</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[21880.22, 26472.75, 19644.48]</t>
+          <t>[21676.06, 27397.95, 32378.8]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[20792.5, 25258.8, 18643.5]</t>
+          <t>[20932.4, 26104.5, 30026.3]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1104.3487347265</v>
+        <v>1608.342811229779</v>
       </c>
       <c r="G149" t="n">
-        <v>1100.881706952231</v>
+        <v>1463.202949201369</v>
       </c>
       <c r="H149" t="n">
-        <v>5.135464829692817</v>
+        <v>5.447452594593372</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[25193.87, 18723.9, 15881.98]</t>
+          <t>[26491.47, 31346.78, 43498.62]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[25258.8, 18643.5, 15494.9]</t>
+          <t>[26104.5, 30026.3, 43388.8]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>231.3068624781027</v>
+        <v>796.9653269131793</v>
       </c>
       <c r="G150" t="n">
-        <v>177.4704541222</v>
+        <v>605.7538227600975</v>
       </c>
       <c r="H150" t="n">
-        <v>1.0621391111216</v>
+        <v>2.04440457848255</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[18765.27, 15917.05, 14973.53]</t>
+          <t>[30908.04, 42916.33, 38332.82]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[18643.5, 15494.9, 14631.7]</t>
+          <t>[30026.3, 43388.8, 37435.4]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>321.3952820801948</v>
+        <v>775.8968949741815</v>
       </c>
       <c r="G151" t="n">
-        <v>295.2485031459212</v>
+        <v>750.5412471515483</v>
       </c>
       <c r="H151" t="n">
-        <v>1.904598666354214</v>
+        <v>2.14090521991233</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[8314.26, 9042.5, 7802.62]</t>
+          <t>[21880.22, 26472.75, 19644.48]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[5901.3, 10161.0, 7304.7]</t>
+          <t>[20792.5, 25258.8, 18643.5]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1562.194152527253</v>
+        <v>1104.3487347265</v>
       </c>
       <c r="G152" t="n">
-        <v>1343.129143702469</v>
+        <v>1100.881706952231</v>
       </c>
       <c r="H152" t="n">
-        <v>19.57097004152264</v>
+        <v>5.135464829692817</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[7147.6, 6237.07, 3032.01]</t>
+          <t>[25193.87, 18723.9, 15881.98]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[10161.0, 7304.7, 3080.6]</t>
+          <t>[25258.8, 18643.5, 15494.9]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1845.963971864735</v>
+        <v>231.3068624781027</v>
       </c>
       <c r="G153" t="n">
-        <v>1376.537827560777</v>
+        <v>177.4704541222</v>
       </c>
       <c r="H153" t="n">
-        <v>15.28312092095038</v>
+        <v>1.0621391111216</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[7659.34, 3690.47, 5869.67]</t>
+          <t>[18765.27, 15917.05, 14973.53]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[7304.7, 3080.6, 6417.0]</t>
+          <t>[18643.5, 15494.9, 14631.7]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>515.5173292844897</v>
+        <v>321.3952820801948</v>
       </c>
       <c r="G154" t="n">
-        <v>503.9451631229931</v>
+        <v>295.2485031459212</v>
       </c>
       <c r="H154" t="n">
-        <v>11.06043077021652</v>
+        <v>1.904598666354214</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[3596.92, 5724.67, 4339.91]</t>
+          <t>[15815.47, 14883.8, 9137.46]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[3080.6, 6417.0, 3776.3]</t>
+          <t>[15494.9, 14631.7, 10947.2]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>595.4172344514943</v>
+        <v>1071.055072514722</v>
       </c>
       <c r="G155" t="n">
-        <v>590.7535545691471</v>
+        <v>794.1353048480923</v>
       </c>
       <c r="H155" t="n">
-        <v>14.15809101685776</v>
+        <v>6.774451136958986</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[5269.81, 4005.22, 7722.51]</t>
+          <t>[14587.1, 8962.68, 8132.52]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[6417.0, 3776.3, 6779.9]</t>
+          <t>[14631.7, 10947.2, 9818.0]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>867.3642803159325</v>
+        <v>1503.459206507316</v>
       </c>
       <c r="G156" t="n">
-        <v>772.9061610718604</v>
+        <v>1238.201183524845</v>
       </c>
       <c r="H156" t="n">
-        <v>12.61411279761353</v>
+        <v>11.86673352898389</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[10853.47, 12957.65, 18481.42]</t>
+          <t>[8987.98, 8153.82, 14627.99]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[13562.1, 13681.1, 16963.3]</t>
+          <t>[10947.2, 9818.0, 16812.4]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1840.72049149162</v>
+        <v>1947.62026892324</v>
       </c>
       <c r="G157" t="n">
-        <v>1650.068310405963</v>
+        <v>1935.935697192788</v>
       </c>
       <c r="H157" t="n">
-        <v>11.40315822192634</v>
+        <v>15.94670419309958</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[15987.68, 22759.0, 26409.91]</t>
+          <t>[9863.91, 17571.84, 21381.83]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[13681.1, 16963.3, 19686.4]</t>
+          <t>[9818.0, 16812.4, 19826.1]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5295.155926473975</v>
+        <v>999.8597180052653</v>
       </c>
       <c r="G158" t="n">
-        <v>4941.929938317737</v>
+        <v>787.0266069147953</v>
       </c>
       <c r="H158" t="n">
-        <v>28.39293012082283</v>
+        <v>4.277205843076704</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[19774.42, 22975.52, 30816.65]</t>
+          <t>[17495.88, 21294.03, 20281.8]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[16963.3, 19686.4, 22567.5]</t>
+          <t>[16812.4, 19826.1, 19147.2]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>5378.016731425882</v>
+        <v>1141.531648704895</v>
       </c>
       <c r="G159" t="n">
-        <v>4783.130871315669</v>
+        <v>1095.337667059179</v>
       </c>
       <c r="H159" t="n">
-        <v>23.2775318302323</v>
+        <v>5.798349731941443</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[19935.41, 26771.1, 32471.16]</t>
+          <t>[20492.33, 19545.13, 27627.23]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[19686.4, 22567.5, 26529.5]</t>
+          <t>[19826.1, 19147.2, 27639.0]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>4204.584653035806</v>
+        <v>448.0858063166625</v>
       </c>
       <c r="G160" t="n">
-        <v>3464.756733571232</v>
+        <v>358.6425468173596</v>
       </c>
       <c r="H160" t="n">
-        <v>14.09603234500707</v>
+        <v>1.827068274271114</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[26460.53, 32098.24, 30885.78]</t>
+          <t>[18933.78, 26793.78, 21965.94]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[22567.5, 26529.5, 26499.9]</t>
+          <t>[19147.2, 27639.0, 21703.2]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>4669.13567084789</v>
+        <v>525.6663145160081</v>
       </c>
       <c r="G161" t="n">
-        <v>4615.883482461828</v>
+        <v>440.4592861744811</v>
       </c>
       <c r="H161" t="n">
-        <v>18.26396874582079</v>
+        <v>1.79443040441295</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[27678.58, 26666.97, 24576.96]</t>
+          <t>[7659.34, 3690.47, 5869.67]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[26529.5, 26499.9, 24757.9]</t>
+          <t>[7304.7, 3080.6, 6417.0]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>678.485742411256</v>
+        <v>515.5173292844897</v>
       </c>
       <c r="G162" t="n">
-        <v>499.0292676628184</v>
+        <v>503.9451631229931</v>
       </c>
       <c r="H162" t="n">
-        <v>1.897537622873662</v>
+        <v>11.06043077021652</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[25622.84, 23622.45, 18200.45]</t>
+          <t>[3596.92, 5724.67, 4339.91]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[26499.9, 24757.9, 20555.9]</t>
+          <t>[3080.6, 6417.0, 3776.3]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1592.337008153752</v>
+        <v>595.4172344514943</v>
       </c>
       <c r="G163" t="n">
-        <v>1455.984311370186</v>
+        <v>590.7535545691471</v>
       </c>
       <c r="H163" t="n">
-        <v>6.451537396071704</v>
+        <v>14.15809101685776</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[24380.33, 18779.28, 16182.5]</t>
+          <t>[5269.81, 4005.22, 7722.51]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[24757.9, 20555.9, 18701.1]</t>
+          <t>[6417.0, 3776.3, 6779.9]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1792.789944674595</v>
+        <v>867.3642803159325</v>
       </c>
       <c r="G164" t="n">
-        <v>1557.598195129411</v>
+        <v>772.9061610718604</v>
       </c>
       <c r="H164" t="n">
-        <v>7.878531796027922</v>
+        <v>12.61411279761353</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[19051.94, 16415.77, 12678.63]</t>
+          <t>[4440.25, 8533.28, 847.31]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[20555.9, 18701.1, 16120.0]</t>
+          <t>[3776.3, 6779.9, 943.6]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2538.218750647952</v>
+        <v>1083.891331392832</v>
       </c>
       <c r="G165" t="n">
-        <v>2410.219574404428</v>
+        <v>837.8763614159565</v>
       </c>
       <c r="H165" t="n">
-        <v>13.62839453570667</v>
+        <v>17.88280480507774</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[17699.21, 13660.28, 13851.3]</t>
+          <t>[7849.93, 781.34, 2173.95]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[18701.1, 16120.0, 17260.2]</t>
+          <t>[6779.9, 943.6, 2536.8]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2494.966960068941</v>
+        <v>659.0283146369003</v>
       </c>
       <c r="G166" t="n">
-        <v>2290.168955707315</v>
+        <v>531.7122680069623</v>
       </c>
       <c r="H166" t="n">
-        <v>13.45541177723815</v>
+        <v>15.76040207754276</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[11715.39, 13928.87, 17723.72]</t>
+          <t>[724.67, 2021.83, 3542.4]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[16696.6, 18055.5, 21519.7]</t>
+          <t>[943.6, 2536.8, 4311.9]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4330.16489353369</v>
+        <v>549.3169080662143</v>
       </c>
       <c r="G167" t="n">
-        <v>4301.272974006402</v>
+        <v>501.1306644518442</v>
       </c>
       <c r="H167" t="n">
-        <v>23.44282720198451</v>
+        <v>20.44900781458211</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[18460.6, 23681.83, 49594.73]</t>
+          <t>[2304.69, 4018.57, 5349.23]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[18055.5, 21519.7, 33545.2]</t>
+          <t>[2536.8, 4311.9, 5524.8]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>9352.830973934617</v>
+        <v>238.5637515252346</v>
       </c>
       <c r="G168" t="n">
-        <v>6205.586609906702</v>
+        <v>233.6667574055959</v>
       </c>
       <c r="H168" t="n">
-        <v>20.04511266058143</v>
+        <v>6.376703456746386</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[23203.86, 48603.66, 57122.26]</t>
+          <t>[4219.81, 5608.79, 7864.36]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[21519.7, 33545.2, 38679.4]</t>
+          <t>[4311.9, 5524.8, 7606.3]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>13780.81570514788</v>
+        <v>165.4595732421756</v>
       </c>
       <c r="G169" t="n">
-        <v>11728.49143131746</v>
+        <v>144.7132335536744</v>
       </c>
       <c r="H169" t="n">
-        <v>33.46583849695281</v>
+        <v>2.349543331468311</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[45385.64, 53372.01, 63877.08]</t>
+          <t>[5671.35, 7948.81, 7573.93]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[33545.2, 38679.4, 45789.2]</t>
+          <t>[5524.8, 7606.3, 5966.7]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>15091.27813348585</v>
+        <v>952.5391516542652</v>
       </c>
       <c r="G170" t="n">
-        <v>14873.64169736669</v>
+        <v>698.7650482120001</v>
       </c>
       <c r="H170" t="n">
-        <v>37.59502839693518</v>
+        <v>11.36410713001019</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[40079.14, 48087.09, 49124.55]</t>
+          <t>[7845.09, 7481.54, 9492.97]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[38679.4, 45789.2, 45191.2]</t>
+          <t>[7606.3, 5966.7, 10042.5]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2751.413859620762</v>
+        <v>940.5239456839843</v>
       </c>
       <c r="G171" t="n">
-        <v>2543.659994535677</v>
+        <v>767.7220627061288</v>
       </c>
       <c r="H171" t="n">
-        <v>5.78034364757967</v>
+        <v>11.33324490640411</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[46462.11, 47478.19, 43967.87]</t>
+          <t>[24380.33, 18779.28, 16182.5]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[45789.2, 45191.2, 43225.3]</t>
+          <t>[24757.9, 20555.9, 18701.1]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1441.590499206543</v>
+        <v>1792.789944674595</v>
       </c>
       <c r="G172" t="n">
-        <v>1234.158437377596</v>
+        <v>1557.598195129411</v>
       </c>
       <c r="H172" t="n">
-        <v>2.749399391908674</v>
+        <v>7.878531796027922</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[46815.85, 43360.67, 39034.91]</t>
+          <t>[19051.94, 16415.77, 12678.63]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[45191.2, 43225.3, 37806.9]</t>
+          <t>[20555.9, 18701.1, 16120.0]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1178.395169160402</v>
+        <v>2538.218750647952</v>
       </c>
       <c r="G173" t="n">
-        <v>996.0131379761709</v>
+        <v>2410.219574404428</v>
       </c>
       <c r="H173" t="n">
-        <v>2.385454859642515</v>
+        <v>13.62839453570667</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[41908.38, 37739.47, 23803.19]</t>
+          <t>[17699.21, 13660.28, 13851.3]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[43225.3, 37806.9, 26249.9]</t>
+          <t>[18701.1, 16120.0, 17260.2]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1604.702068546445</v>
+        <v>2494.966960068941</v>
       </c>
       <c r="G174" t="n">
-        <v>1277.018392864139</v>
+        <v>2290.168955707315</v>
       </c>
       <c r="H174" t="n">
-        <v>4.1819375600617</v>
+        <v>13.45541177723815</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[38879.82, 24515.82, 16032.13]</t>
+          <t>[14426.71, 14621.31, 10189.73]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[37806.9, 26249.9, 20416.9]</t>
+          <t>[16120.0, 17260.2, 15361.5]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2791.9161138388</v>
+        <v>3491.80981493549</v>
       </c>
       <c r="G175" t="n">
-        <v>2397.254792696076</v>
+        <v>3167.984231016493</v>
       </c>
       <c r="H175" t="n">
-        <v>10.3067007081636</v>
+        <v>19.8200867583891</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[23865.06, 15609.94, 17345.1]</t>
+          <t>[16321.35, 11363.04, 13334.2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[26249.9, 20416.9, 23407.5]</t>
+          <t>[17260.2, 15361.5, 15701.3]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>4674.293951737754</v>
+        <v>2736.925611365405</v>
       </c>
       <c r="G176" t="n">
-        <v>4418.067467276926</v>
+        <v>2434.803465724165</v>
       </c>
       <c r="H176" t="n">
-        <v>19.50952335631319</v>
+        <v>15.51477192775421</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[21148.56, 23546.71, 30935.44]</t>
+          <t>[12010.59, 14088.13, 19797.9]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[26380.9, 29132.2, 36655.4]</t>
+          <t>[15361.5, 15701.3, 19059.0]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5516.431613396662</v>
+        <v>2189.132922278429</v>
       </c>
       <c r="G177" t="n">
-        <v>5512.597591637804</v>
+        <v>1900.994824453638</v>
       </c>
       <c r="H177" t="n">
-        <v>18.20380803392137</v>
+        <v>11.98824690489496</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[29267.12, 38320.42, 45723.17]</t>
+          <t>[17945.2, 25166.61, 29172.38]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[29132.2, 36655.4, 42594.0]</t>
+          <t>[15701.3, 19059.0, 21595.3]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2047.939760483971</v>
+        <v>5766.28840512032</v>
       </c>
       <c r="G178" t="n">
-        <v>1643.033090049961</v>
+        <v>5309.53400627369</v>
       </c>
       <c r="H178" t="n">
-        <v>4.117320706888105</v>
+        <v>27.14125133005259</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[38147.36, 45519.5, 55244.27]</t>
+          <t>[22165.18, 25718.76, 33917.41]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[36655.4, 42594.0, 50949.5]</t>
+          <t>[19059.0, 21595.3, 23858.2]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3121.409077395667</v>
+        <v>6527.864161364804</v>
       </c>
       <c r="G179" t="n">
-        <v>2904.078612852735</v>
+        <v>5762.949653443713</v>
       </c>
       <c r="H179" t="n">
-        <v>6.456016045911067</v>
+        <v>25.8514767070557</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[43766.0, 53149.97, 55622.19]</t>
+          <t>[22219.72, 29336.74, 35432.13]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[42594.0, 50949.5, 54824.2]</t>
+          <t>[21595.3, 23858.2, 29471.7]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1511.341175986275</v>
+        <v>4687.964940499991</v>
       </c>
       <c r="G180" t="n">
-        <v>1390.155557473185</v>
+        <v>4021.130290139648</v>
       </c>
       <c r="H180" t="n">
-        <v>2.842014279621929</v>
+        <v>15.3595455156562</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[51750.51, 54182.93, 43428.33]</t>
+          <t>[28532.9, 34467.37, 33254.79]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[50949.5, 54824.2, 39643.3]</t>
+          <t>[23858.2, 29471.7, 28373.2]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2264.162126546037</v>
+        <v>4852.471652910778</v>
       </c>
       <c r="G181" t="n">
-        <v>1742.436333873557</v>
+        <v>4850.652711275266</v>
       </c>
       <c r="H181" t="n">
-        <v>4.096521037931972</v>
+        <v>17.91644757969962</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[53357.54, 42776.63, 39662.46]</t>
+          <t>[41908.38, 37739.47, 23803.19]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[54824.2, 39643.3, 38641.4]</t>
+          <t>[43225.3, 37806.9, 26249.9]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2082.576730280687</v>
+        <v>1604.702068546445</v>
       </c>
       <c r="G182" t="n">
-        <v>1873.680793269159</v>
+        <v>1277.018392864139</v>
       </c>
       <c r="H182" t="n">
-        <v>4.40713176046684</v>
+        <v>4.1819375600617</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[43935.52, 40722.43, 37328.09]</t>
+          <t>[38879.82, 24515.82, 16032.13]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[39643.3, 38641.4, 35950.3]</t>
+          <t>[37806.9, 26249.9, 20416.9]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2866.600640305101</v>
+        <v>2791.9161138388</v>
       </c>
       <c r="G183" t="n">
-        <v>2583.682948665621</v>
+        <v>2397.254792696076</v>
       </c>
       <c r="H183" t="n">
-        <v>6.681700858134134</v>
+        <v>10.3067007081636</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[36787.97, 33759.67, 29843.29]</t>
+          <t>[23865.06, 15609.94, 17345.1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[38641.4, 35950.3, 32936.5]</t>
+          <t>[26249.9, 20416.9, 23407.5]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2435.980954600679</v>
+        <v>4674.293951737754</v>
       </c>
       <c r="G184" t="n">
-        <v>2379.090129088245</v>
+        <v>4418.067467276926</v>
       </c>
       <c r="H184" t="n">
-        <v>6.760472899455867</v>
+        <v>19.50952335631319</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[35442.75, 31314.24, 29350.76]</t>
+          <t>[17100.46, 18985.08, 11715.52]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[35950.3, 32936.5, 30760.6]</t>
+          <t>[20416.9, 23407.5, 17844.5]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1275.013561828149</v>
+        <v>4765.183645082959</v>
       </c>
       <c r="G185" t="n">
-        <v>1179.882269280857</v>
+        <v>4622.612106611778</v>
       </c>
       <c r="H185" t="n">
-        <v>3.64016097850134</v>
+        <v>23.16112223323545</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[22621.11, 13938.67, 15703.86]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[23407.5, 17844.5, 18781.6]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>2906.682115530893</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2589.987980181338</v>
+      </c>
+      <c r="H186" t="n">
+        <v>13.87824026623173</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[14416.36, 16235.57, 20698.02]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[17844.5, 18781.6, 22952.8]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>2787.975170189041</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2742.981650012165</v>
+      </c>
+      <c r="H187" t="n">
+        <v>14.19689675567211</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[20060.39, 25528.87, 51872.63]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[18781.6, 22952.8, 34340.3]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>10257.58093876852</v>
+      </c>
+      <c r="G188" t="n">
+        <v>7129.061038226122</v>
+      </c>
+      <c r="H188" t="n">
+        <v>23.02890847645139</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[23917.11, 48618.28, 57012.99]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[22952.8, 34340.3, 38714.8]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>13411.61688972009</v>
+      </c>
+      <c r="G189" t="n">
+        <v>11180.16160788103</v>
+      </c>
+      <c r="H189" t="n">
+        <v>31.01442513801625</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[46677.05, 54752.44, 65419.29]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[34340.3, 38714.8, 45201.5]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>16514.23945312277</v>
+      </c>
+      <c r="G190" t="n">
+        <v>16197.39369036984</v>
+      </c>
+      <c r="H190" t="n">
+        <v>40.69274151319708</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[40376.63, 48360.98, 49213.85]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[38714.8, 45201.5, 46680.7]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>2527.243978379114</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2451.489469464934</v>
+      </c>
+      <c r="H191" t="n">
+        <v>5.569608832034916</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[36787.97, 33759.67, 29843.29]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[38641.4, 35950.3, 32936.5]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>2435.980954600679</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2379.090129088245</v>
+      </c>
+      <c r="H192" t="n">
+        <v>6.760472899455867</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[35442.75, 31314.24, 29350.76]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[35950.3, 32936.5, 30760.6]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1275.013561828149</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1179.882269280857</v>
+      </c>
+      <c r="H193" t="n">
+        <v>3.64016097850134</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[31756.13, 29759.42, 29143.14]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[32936.5, 30760.6, 28616.8]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>943.8663177732021</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>902.6268211935507</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>2.892586997130032</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[30851.7, 30200.4, 25047.47]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[30760.6, 28616.8, 33158.0]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>4771.330332631107</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3261.741449466796</v>
+      </c>
+      <c r="H195" t="n">
+        <v>10.0967340548655</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[30111.42, 24975.39, 27709.26]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[28616.8, 33158.0, 35623.7]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>6628.908942360872</v>
+      </c>
+      <c r="G196" t="n">
+        <v>5863.889437688587</v>
+      </c>
+      <c r="H196" t="n">
+        <v>17.37242979936136</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[23750.42, 26365.58, 34344.46]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[33158.0, 35623.7, 44086.4]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>9471.373306020108</v>
+      </c>
+      <c r="G197" t="n">
+        <v>9469.213291716256</v>
+      </c>
+      <c r="H197" t="n">
+        <v>25.48600462243693</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[36652.5, 47538.7, 56311.11]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[35623.7, 44086.4, 49990.5]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>4200.277095417615</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3600.5726397007</v>
+      </c>
+      <c r="H198" t="n">
+        <v>7.787454860396685</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[46231.24, 54782.31, 66156.84]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[44086.4, 49990.5, 59303.1]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>4984.495455703833</v>
+      </c>
+      <c r="G199" t="n">
+        <v>4596.798638598714</v>
+      </c>
+      <c r="H199" t="n">
+        <v>8.669224166453475</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[52285.58, 63179.24, 66262.24]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[49990.5, 59303.1, 61702.9]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>3700.427485176406</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3576.855167536853</v>
+      </c>
+      <c r="H200" t="n">
+        <v>6.172124657181477</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[60449.86, 63440.39, 50013.08]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[59303.1, 61702.9, 43495.5]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>3950.222547927719</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3133.942324864816</v>
+      </c>
+      <c r="H201" t="n">
+        <v>6.578037101451671</v>
       </c>
     </row>
   </sheetData>
